--- a/РАБОЧИЙ СТОЛ/расчеты ПОКОМ КИ/дв 01,10,26 мррсч пок ки.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты ПОКОМ КИ/дв 01,10,26 мррсч пок ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03808A2-1849-4912-8D44-3E4CE24FBC42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E1D2F4-D245-4EED-A628-43EFE50E0B94}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,12 +18,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$Z$131</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="167">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -71,9 +79,6 @@
   </si>
   <si>
     <t>ср нов</t>
-  </si>
-  <si>
-    <t>расчет</t>
   </si>
   <si>
     <t>кон ост</t>
@@ -532,9 +537,20 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
       </rPr>
       <t xml:space="preserve"> / ПРОМО сентябрь</t>
     </r>
+  </si>
+  <si>
+    <t>заказ</t>
+  </si>
+  <si>
+    <t>05,10,</t>
+  </si>
+  <si>
+    <t>нет потребности / нет в бланке</t>
   </si>
 </sst>
 </file>
@@ -555,22 +571,30 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
@@ -1168,25 +1192,25 @@
         <v>15</v>
       </c>
       <c r="T3" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="U3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="V3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="W3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="X3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="X3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y3" s="2" t="s">
+      <c r="Z3" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
@@ -1228,28 +1252,30 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="S4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="S4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T4" s="1"/>
+      <c r="T4" s="1" t="s">
+        <v>165</v>
+      </c>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
@@ -1347,7 +1373,7 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="4">
         <f>SUM(Z6:Z480)</f>
-        <v>2667.7998180055629</v>
+        <v>2670</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
@@ -1375,10 +1401,10 @@
     </row>
     <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="C6" s="1">
         <v>6.0830000000000002</v>
@@ -1399,7 +1425,7 @@
         <v>50</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1">
@@ -1442,7 +1468,7 @@
       </c>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1">
-        <f>G6*T6</f>
+        <f>ROUND(G6*T6,0)</f>
         <v>0</v>
       </c>
       <c r="AA6" s="1"/>
@@ -1471,10 +1497,10 @@
     </row>
     <row r="7" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" s="1">
         <v>164.81800000000001</v>
@@ -1495,7 +1521,7 @@
         <v>45</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1">
@@ -1537,10 +1563,10 @@
         <v>21.689</v>
       </c>
       <c r="Y7" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Z7" s="1">
-        <f>G7*T7</f>
+        <f t="shared" ref="Z7:Z70" si="5">ROUND(G7*T7,0)</f>
         <v>0</v>
       </c>
       <c r="AA7" s="1"/>
@@ -1569,10 +1595,10 @@
     </row>
     <row r="8" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="1">
         <v>237.28100000000001</v>
@@ -1593,7 +1619,7 @@
         <v>45</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1">
@@ -1640,7 +1666,7 @@
       </c>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1">
-        <f>G8*T8</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AA8" s="1"/>
@@ -1669,10 +1695,10 @@
     </row>
     <row r="9" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>34</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
@@ -1683,7 +1709,7 @@
       </c>
       <c r="H9" s="10"/>
       <c r="I9" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
@@ -1721,9 +1747,12 @@
         <v>0</v>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z9" s="10"/>
+        <v>34</v>
+      </c>
+      <c r="Z9" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AA9" s="1"/>
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
@@ -1750,10 +1779,10 @@
     </row>
     <row r="10" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1">
@@ -1772,7 +1801,7 @@
         <v>45</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1">
@@ -1815,7 +1844,7 @@
       </c>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1">
-        <f t="shared" ref="Z10:Z17" si="5">G10*T10</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA10" s="1"/>
@@ -1844,10 +1873,10 @@
     </row>
     <row r="11" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1">
         <v>595</v>
@@ -1868,7 +1897,7 @@
         <v>45</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1">
@@ -1895,7 +1924,7 @@
         <v>82.6</v>
       </c>
       <c r="T11" s="5">
-        <f t="shared" ref="T10:T17" si="6">12*S11-R11-Q11-P11-O11-F11</f>
+        <f t="shared" ref="T11:T17" si="6">12*S11-R11-Q11-P11-O11-F11</f>
         <v>342.29294306335203</v>
       </c>
       <c r="U11" s="1">
@@ -1915,7 +1944,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1">
         <f t="shared" si="5"/>
-        <v>154.03182437850842</v>
+        <v>154</v>
       </c>
       <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
@@ -1943,10 +1972,10 @@
     </row>
     <row r="12" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1">
         <v>2</v>
@@ -1967,7 +1996,7 @@
         <v>180</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1">
@@ -2039,10 +2068,10 @@
     </row>
     <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1">
@@ -2061,7 +2090,7 @@
         <v>40</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1">
@@ -2108,7 +2137,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1">
         <f t="shared" si="5"/>
-        <v>5.5526701570680599</v>
+        <v>6</v>
       </c>
       <c r="AA13" s="1"/>
       <c r="AB13" s="1"/>
@@ -2136,10 +2165,10 @@
     </row>
     <row r="14" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1">
         <v>242</v>
@@ -2160,7 +2189,7 @@
         <v>180</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1">
@@ -2207,7 +2236,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1">
         <f t="shared" si="5"/>
-        <v>1.802000000000004</v>
+        <v>2</v>
       </c>
       <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
@@ -2235,10 +2264,10 @@
     </row>
     <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C15" s="1">
         <v>-9.9909999999999997</v>
@@ -2259,7 +2288,7 @@
         <v>70</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1">
@@ -2331,10 +2360,10 @@
     </row>
     <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16" s="1">
         <v>1086.145</v>
@@ -2355,7 +2384,7 @@
         <v>50</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1">
@@ -2402,7 +2431,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1">
         <f t="shared" si="5"/>
-        <v>348.0912000000003</v>
+        <v>348</v>
       </c>
       <c r="AA16" s="1"/>
       <c r="AB16" s="1"/>
@@ -2430,10 +2459,10 @@
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C17" s="1">
         <v>88.183999999999997</v>
@@ -2454,7 +2483,7 @@
         <v>60</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1">
@@ -2501,7 +2530,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1">
         <f t="shared" si="5"/>
-        <v>34.571600000000004</v>
+        <v>35</v>
       </c>
       <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
@@ -2529,10 +2558,10 @@
     </row>
     <row r="18" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
@@ -2547,7 +2576,7 @@
       </c>
       <c r="H18" s="10"/>
       <c r="I18" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J18" s="10"/>
       <c r="K18" s="10">
@@ -2585,7 +2614,10 @@
         <v>0</v>
       </c>
       <c r="Y18" s="10"/>
-      <c r="Z18" s="10"/>
+      <c r="Z18" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
@@ -2612,10 +2644,10 @@
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
@@ -2630,10 +2662,10 @@
       </c>
       <c r="H19" s="10"/>
       <c r="I19" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K19" s="10">
         <v>12.5</v>
@@ -2670,7 +2702,10 @@
         <v>0</v>
       </c>
       <c r="Y19" s="10"/>
-      <c r="Z19" s="10"/>
+      <c r="Z19" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
@@ -2697,10 +2732,10 @@
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20" s="1">
         <v>16.09</v>
@@ -2721,7 +2756,7 @@
         <v>60</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1">
@@ -2764,7 +2799,7 @@
       </c>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1">
-        <f>G20*T20</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA20" s="1"/>
@@ -2793,10 +2828,10 @@
     </row>
     <row r="21" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C21" s="1">
         <v>33.39</v>
@@ -2817,7 +2852,7 @@
         <v>180</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1">
@@ -2859,10 +2894,10 @@
         <v>0.43280000000000002</v>
       </c>
       <c r="Y21" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Z21" s="1">
-        <f>G21*T21</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA21" s="1"/>
@@ -2891,10 +2926,10 @@
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="1">
         <v>90.322999999999993</v>
@@ -2915,7 +2950,7 @@
         <v>60</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1">
@@ -2958,7 +2993,7 @@
       </c>
       <c r="Y22" s="1"/>
       <c r="Z22" s="1">
-        <f>G22*T22</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA22" s="1"/>
@@ -2987,10 +3022,10 @@
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
@@ -3005,10 +3040,10 @@
       </c>
       <c r="H23" s="10"/>
       <c r="I23" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K23" s="10">
         <v>25</v>
@@ -3045,7 +3080,10 @@
         <v>0</v>
       </c>
       <c r="Y23" s="10"/>
-      <c r="Z23" s="10"/>
+      <c r="Z23" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
@@ -3072,10 +3110,10 @@
     </row>
     <row r="24" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C24" s="1">
         <v>18.47</v>
@@ -3096,7 +3134,7 @@
         <v>70</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1">
@@ -3123,7 +3161,7 @@
         <v>13.150600000000001</v>
       </c>
       <c r="T24" s="5">
-        <f t="shared" ref="T24:T27" si="7">12*S24-R24-Q24-P24-O24-F24</f>
+        <f t="shared" ref="T24:T25" si="7">12*S24-R24-Q24-P24-O24-F24</f>
         <v>51.844200000000029</v>
       </c>
       <c r="U24" s="1">
@@ -3142,8 +3180,8 @@
       </c>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1">
-        <f>G24*T24</f>
-        <v>51.844200000000029</v>
+        <f t="shared" si="5"/>
+        <v>52</v>
       </c>
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
@@ -3171,10 +3209,10 @@
     </row>
     <row r="25" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C25" s="1">
         <v>27.087</v>
@@ -3195,7 +3233,7 @@
         <v>70</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1">
@@ -3240,11 +3278,11 @@
         <v>22.914000000000001</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z25" s="1">
-        <f>G25*T25</f>
-        <v>17.319600000000033</v>
+        <f t="shared" si="5"/>
+        <v>17</v>
       </c>
       <c r="AA25" s="1"/>
       <c r="AB25" s="1"/>
@@ -3272,10 +3310,10 @@
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26" s="1">
         <v>32.575000000000003</v>
@@ -3296,7 +3334,7 @@
         <v>180</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1">
@@ -3338,10 +3376,10 @@
         <v>0.34420000000000001</v>
       </c>
       <c r="Y26" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Z26" s="1">
-        <f>G26*T26</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA26" s="1"/>
@@ -3370,10 +3408,10 @@
     </row>
     <row r="27" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C27" s="1">
         <v>0.63600000000000001</v>
@@ -3394,7 +3432,7 @@
         <v>70</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1">
@@ -3438,10 +3476,10 @@
         <v>18.1692</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z27" s="1">
-        <f>G27*T27</f>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="AA27" s="1"/>
@@ -3470,10 +3508,10 @@
     </row>
     <row r="28" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="10"/>
@@ -3484,7 +3522,7 @@
       </c>
       <c r="H28" s="10"/>
       <c r="I28" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J28" s="10"/>
       <c r="K28" s="10"/>
@@ -3522,9 +3560,12 @@
         <v>0</v>
       </c>
       <c r="Y28" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z28" s="10"/>
+        <v>34</v>
+      </c>
+      <c r="Z28" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
@@ -3551,10 +3592,10 @@
     </row>
     <row r="29" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C29" s="1">
         <v>16.323</v>
@@ -3573,7 +3614,7 @@
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J29" s="1"/>
       <c r="K29" s="1">
@@ -3600,7 +3641,7 @@
         <v>4.5697999999999999</v>
       </c>
       <c r="T29" s="5">
-        <f t="shared" ref="T29:T35" si="8">12*S29-R29-Q29-P29-O29-F29</f>
+        <f t="shared" ref="T29:T32" si="8">12*S29-R29-Q29-P29-O29-F29</f>
         <v>14.713387031064098</v>
       </c>
       <c r="U29" s="1">
@@ -3619,8 +3660,8 @@
       </c>
       <c r="Y29" s="1"/>
       <c r="Z29" s="1">
-        <f t="shared" ref="Z29:Z35" si="9">G29*T29</f>
-        <v>14.713387031064098</v>
+        <f t="shared" si="5"/>
+        <v>15</v>
       </c>
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
@@ -3648,10 +3689,10 @@
     </row>
     <row r="30" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -3664,7 +3705,7 @@
         <v>40</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -3705,7 +3746,7 @@
       </c>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA30" s="1"/>
@@ -3734,10 +3775,10 @@
     </row>
     <row r="31" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C31" s="1">
         <v>48.945999999999998</v>
@@ -3758,7 +3799,7 @@
         <v>30</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1">
@@ -3801,7 +3842,7 @@
       </c>
       <c r="Y31" s="1"/>
       <c r="Z31" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA31" s="1"/>
@@ -3830,10 +3871,10 @@
     </row>
     <row r="32" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C32" s="1">
         <v>26.748000000000001</v>
@@ -3854,7 +3895,7 @@
         <v>40</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J32" s="1"/>
       <c r="K32" s="1">
@@ -3900,8 +3941,8 @@
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1">
-        <f t="shared" si="9"/>
-        <v>357.00320000000011</v>
+        <f t="shared" si="5"/>
+        <v>357</v>
       </c>
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
@@ -3929,10 +3970,10 @@
     </row>
     <row r="33" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -3945,7 +3986,7 @@
         <v>40</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J33" s="1"/>
       <c r="K33" s="1">
@@ -3990,7 +4031,7 @@
       </c>
       <c r="Y33" s="1"/>
       <c r="Z33" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="AA33" s="1"/>
@@ -4019,10 +4060,10 @@
     </row>
     <row r="34" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C34" s="1">
         <v>40.838999999999999</v>
@@ -4041,7 +4082,7 @@
         <v>30</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J34" s="1"/>
       <c r="K34" s="1">
@@ -4085,10 +4126,10 @@
         <v>0</v>
       </c>
       <c r="Y34" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Z34" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA34" s="1"/>
@@ -4117,10 +4158,10 @@
     </row>
     <row r="35" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1">
@@ -4139,7 +4180,7 @@
         <v>50</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1">
@@ -4181,10 +4222,10 @@
         <v>-0.1764</v>
       </c>
       <c r="Y35" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z35" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA35" s="1"/>
@@ -4213,10 +4254,10 @@
     </row>
     <row r="36" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C36" s="10"/>
       <c r="D36" s="10"/>
@@ -4231,7 +4272,7 @@
       </c>
       <c r="H36" s="10"/>
       <c r="I36" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J36" s="10"/>
       <c r="K36" s="10">
@@ -4269,7 +4310,10 @@
         <v>0</v>
       </c>
       <c r="Y36" s="10"/>
-      <c r="Z36" s="10"/>
+      <c r="Z36" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
@@ -4296,10 +4340,10 @@
     </row>
     <row r="37" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
@@ -4318,7 +4362,7 @@
         <v>50</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J37" s="1"/>
       <c r="K37" s="1">
@@ -4361,7 +4405,7 @@
       </c>
       <c r="Y37" s="1"/>
       <c r="Z37" s="1">
-        <f t="shared" ref="Z37:Z71" si="10">G37*T37</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA37" s="1"/>
@@ -4390,10 +4434,10 @@
     </row>
     <row r="38" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C38" s="1">
         <v>14</v>
@@ -4414,14 +4458,14 @@
         <v>45</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J38" s="1"/>
       <c r="K38" s="1">
         <v>567</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="11">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="9">E38-K38</f>
         <v>-434</v>
       </c>
       <c r="M38" s="1"/>
@@ -4437,18 +4481,18 @@
         <v>300</v>
       </c>
       <c r="S38" s="1">
-        <f t="shared" ref="S38:S69" si="12">E38/5</f>
+        <f t="shared" ref="S38:S69" si="10">E38/5</f>
         <v>26.6</v>
       </c>
       <c r="T38" s="5">
         <v>200</v>
       </c>
       <c r="U38" s="1">
-        <f t="shared" ref="U38:U69" si="13">(F38+O38+P38+Q38+R38+T38)/S38</f>
+        <f t="shared" ref="U38:U69" si="11">(F38+O38+P38+Q38+R38+T38)/S38</f>
         <v>38.096396258668847</v>
       </c>
       <c r="V38" s="1">
-        <f t="shared" ref="V38:V69" si="14">(F38+O38+P38+Q38+R38)/S38</f>
+        <f t="shared" ref="V38:V69" si="12">(F38+O38+P38+Q38+R38)/S38</f>
         <v>30.577599266187647</v>
       </c>
       <c r="W38" s="1">
@@ -4459,7 +4503,7 @@
       </c>
       <c r="Y38" s="1"/>
       <c r="Z38" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>80</v>
       </c>
       <c r="AA38" s="1"/>
@@ -4488,10 +4532,10 @@
     </row>
     <row r="39" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C39" s="1">
         <v>621</v>
@@ -4512,14 +4556,14 @@
         <v>50</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1">
         <v>197</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
       <c r="M39" s="1"/>
@@ -4535,19 +4579,19 @@
         <v>0</v>
       </c>
       <c r="S39" s="1">
+        <f t="shared" si="10"/>
+        <v>42.2</v>
+      </c>
+      <c r="T39" s="5">
+        <f t="shared" ref="T39:T66" si="13">12*S39-R39-Q39-P39-O39-F39</f>
+        <v>127.40000000000003</v>
+      </c>
+      <c r="U39" s="1">
+        <f t="shared" si="11"/>
+        <v>12</v>
+      </c>
+      <c r="V39" s="1">
         <f t="shared" si="12"/>
-        <v>42.2</v>
-      </c>
-      <c r="T39" s="5">
-        <f t="shared" ref="T37:T71" si="15">12*S39-R39-Q39-P39-O39-F39</f>
-        <v>127.40000000000003</v>
-      </c>
-      <c r="U39" s="1">
-        <f t="shared" si="13"/>
-        <v>12</v>
-      </c>
-      <c r="V39" s="1">
-        <f t="shared" si="14"/>
         <v>8.9810426540284354</v>
       </c>
       <c r="W39" s="1">
@@ -4558,8 +4602,8 @@
       </c>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1">
-        <f t="shared" si="10"/>
-        <v>57.33000000000002</v>
+        <f t="shared" si="5"/>
+        <v>57</v>
       </c>
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
@@ -4587,10 +4631,10 @@
     </row>
     <row r="40" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C40" s="1">
         <v>-3</v>
@@ -4611,14 +4655,14 @@
         <v>45</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1">
         <v>380</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-227</v>
       </c>
       <c r="M40" s="1"/>
@@ -4634,18 +4678,18 @@
         <v>250</v>
       </c>
       <c r="S40" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>30.6</v>
       </c>
       <c r="T40" s="5">
         <v>150</v>
       </c>
       <c r="U40" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>22.320261437908496</v>
       </c>
       <c r="V40" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>17.41830065359477</v>
       </c>
       <c r="W40" s="1">
@@ -4656,7 +4700,7 @@
       </c>
       <c r="Y40" s="1"/>
       <c r="Z40" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="AA40" s="1"/>
@@ -4685,10 +4729,10 @@
     </row>
     <row r="41" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1">
@@ -4707,14 +4751,14 @@
         <v>40</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J41" s="1"/>
       <c r="K41" s="1">
         <v>124</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-52</v>
       </c>
       <c r="M41" s="1"/>
@@ -4730,18 +4774,18 @@
         <v>60</v>
       </c>
       <c r="S41" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>14.4</v>
       </c>
       <c r="T41" s="5">
         <v>50</v>
       </c>
       <c r="U41" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>18.91795865633075</v>
       </c>
       <c r="V41" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>15.445736434108529</v>
       </c>
       <c r="W41" s="1">
@@ -4752,7 +4796,7 @@
       </c>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="AA41" s="1"/>
@@ -4781,10 +4825,10 @@
     </row>
     <row r="42" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C42" s="1">
         <v>34.137999999999998</v>
@@ -4805,14 +4849,14 @@
         <v>45</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J42" s="1"/>
       <c r="K42" s="1">
         <v>1.6</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-0.19600000000000017</v>
       </c>
       <c r="M42" s="1"/>
@@ -4828,16 +4872,16 @@
         <v>0</v>
       </c>
       <c r="S42" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0.28079999999999999</v>
       </c>
       <c r="T42" s="5"/>
       <c r="U42" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>184.98389186213572</v>
       </c>
       <c r="V42" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>184.98389186213572</v>
       </c>
       <c r="W42" s="1">
@@ -4847,10 +4891,10 @@
         <v>0.86159999999999992</v>
       </c>
       <c r="Y42" s="15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Z42" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA42" s="1"/>
@@ -4879,10 +4923,10 @@
     </row>
     <row r="43" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C43" s="1">
         <v>132</v>
@@ -4903,14 +4947,14 @@
         <v>731</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J43" s="1"/>
       <c r="K43" s="1">
         <v>32</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
       <c r="M43" s="1"/>
@@ -4926,16 +4970,16 @@
         <v>0</v>
       </c>
       <c r="S43" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>7.4</v>
       </c>
       <c r="T43" s="5"/>
       <c r="U43" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>49.09779344561953</v>
       </c>
       <c r="V43" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>49.09779344561953</v>
       </c>
       <c r="W43" s="1">
@@ -4945,10 +4989,10 @@
         <v>6.6</v>
       </c>
       <c r="Y43" s="15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Z43" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA43" s="1"/>
@@ -4977,10 +5021,10 @@
     </row>
     <row r="44" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -4993,14 +5037,14 @@
         <v>40</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J44" s="1"/>
       <c r="K44" s="1">
         <v>2</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-2</v>
       </c>
       <c r="M44" s="1"/>
@@ -5016,16 +5060,16 @@
         <v>60</v>
       </c>
       <c r="S44" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="T44" s="5"/>
       <c r="U44" s="1" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V44" s="1" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W44" s="1">
@@ -5036,7 +5080,7 @@
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA44" s="1"/>
@@ -5065,10 +5109,10 @@
     </row>
     <row r="45" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1">
@@ -5087,14 +5131,14 @@
         <v>40</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J45" s="1"/>
       <c r="K45" s="1">
         <v>40</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-10.478999999999999</v>
       </c>
       <c r="M45" s="1"/>
@@ -5110,18 +5154,18 @@
         <v>0</v>
       </c>
       <c r="S45" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>5.9042000000000003</v>
       </c>
       <c r="T45" s="5">
         <v>10</v>
       </c>
       <c r="U45" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>16.127647335105895</v>
       </c>
       <c r="V45" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>14.433937772421704</v>
       </c>
       <c r="W45" s="1">
@@ -5131,10 +5175,10 @@
         <v>0</v>
       </c>
       <c r="Y45" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z45" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="AA45" s="1"/>
@@ -5163,10 +5207,10 @@
     </row>
     <row r="46" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C46" s="1">
         <v>2</v>
@@ -5185,14 +5229,14 @@
         <v>40</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J46" s="1"/>
       <c r="K46" s="1">
         <v>114</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-109</v>
       </c>
       <c r="M46" s="1"/>
@@ -5208,16 +5252,16 @@
         <v>150</v>
       </c>
       <c r="S46" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="T46" s="5"/>
       <c r="U46" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>411.70383275261327</v>
       </c>
       <c r="V46" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>411.70383275261327</v>
       </c>
       <c r="W46" s="1">
@@ -5228,7 +5272,7 @@
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA46" s="1"/>
@@ -5257,10 +5301,10 @@
     </row>
     <row r="47" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C47" s="1">
         <v>25</v>
@@ -5281,14 +5325,14 @@
         <v>45</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J47" s="1"/>
       <c r="K47" s="1">
         <v>104</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-90</v>
       </c>
       <c r="M47" s="1"/>
@@ -5304,16 +5348,16 @@
         <v>0</v>
       </c>
       <c r="S47" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>2.8</v>
       </c>
       <c r="T47" s="5"/>
       <c r="U47" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>70.889212827988359</v>
       </c>
       <c r="V47" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>70.889212827988359</v>
       </c>
       <c r="W47" s="1">
@@ -5324,7 +5368,7 @@
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA47" s="1"/>
@@ -5353,10 +5397,10 @@
     </row>
     <row r="48" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1">
@@ -5375,14 +5419,14 @@
         <v>40</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J48" s="1"/>
       <c r="K48" s="1">
         <v>80</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-11.816999999999993</v>
       </c>
       <c r="M48" s="1"/>
@@ -5398,19 +5442,19 @@
         <v>20</v>
       </c>
       <c r="S48" s="1">
+        <f t="shared" si="10"/>
+        <v>13.636600000000001</v>
+      </c>
+      <c r="T48" s="5">
+        <f t="shared" si="13"/>
+        <v>52.641200000000012</v>
+      </c>
+      <c r="U48" s="1">
+        <f t="shared" si="11"/>
+        <v>12</v>
+      </c>
+      <c r="V48" s="1">
         <f t="shared" si="12"/>
-        <v>13.636600000000001</v>
-      </c>
-      <c r="T48" s="5">
-        <f t="shared" si="15"/>
-        <v>52.641200000000012</v>
-      </c>
-      <c r="U48" s="1">
-        <f t="shared" si="13"/>
-        <v>12</v>
-      </c>
-      <c r="V48" s="1">
-        <f t="shared" si="14"/>
         <v>8.1397122449877539</v>
       </c>
       <c r="W48" s="1">
@@ -5420,11 +5464,11 @@
         <v>0</v>
       </c>
       <c r="Y48" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z48" s="1">
-        <f t="shared" si="10"/>
-        <v>52.641200000000012</v>
+        <f t="shared" si="5"/>
+        <v>53</v>
       </c>
       <c r="AA48" s="1"/>
       <c r="AB48" s="1"/>
@@ -5452,10 +5496,10 @@
     </row>
     <row r="49" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -5468,14 +5512,14 @@
         <v>40</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J49" s="1"/>
       <c r="K49" s="1">
         <v>37</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-37</v>
       </c>
       <c r="M49" s="1"/>
@@ -5493,16 +5537,16 @@
         <v>250</v>
       </c>
       <c r="S49" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="T49" s="5"/>
       <c r="U49" s="1" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V49" s="1" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W49" s="1">
@@ -5513,7 +5557,7 @@
       </c>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA49" s="1"/>
@@ -5542,10 +5586,10 @@
     </row>
     <row r="50" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C50" s="1">
         <v>394</v>
@@ -5566,14 +5610,14 @@
         <v>40</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J50" s="1"/>
       <c r="K50" s="1">
         <v>215</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-3</v>
       </c>
       <c r="M50" s="1"/>
@@ -5589,19 +5633,19 @@
         <v>141.19999999999999</v>
       </c>
       <c r="S50" s="1">
+        <f t="shared" si="10"/>
+        <v>42.4</v>
+      </c>
+      <c r="T50" s="5">
+        <f t="shared" si="13"/>
+        <v>201.59999999999997</v>
+      </c>
+      <c r="U50" s="1">
+        <f t="shared" si="11"/>
+        <v>12</v>
+      </c>
+      <c r="V50" s="1">
         <f t="shared" si="12"/>
-        <v>42.4</v>
-      </c>
-      <c r="T50" s="5">
-        <f t="shared" si="15"/>
-        <v>201.59999999999997</v>
-      </c>
-      <c r="U50" s="1">
-        <f t="shared" si="13"/>
-        <v>12</v>
-      </c>
-      <c r="V50" s="1">
-        <f t="shared" si="14"/>
         <v>7.2452830188679247</v>
       </c>
       <c r="W50" s="1">
@@ -5612,8 +5656,8 @@
       </c>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1">
-        <f t="shared" si="10"/>
-        <v>80.639999999999986</v>
+        <f t="shared" si="5"/>
+        <v>81</v>
       </c>
       <c r="AA50" s="1"/>
       <c r="AB50" s="1"/>
@@ -5641,10 +5685,10 @@
     </row>
     <row r="51" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C51" s="1">
         <v>-4.0789999999999997</v>
@@ -5663,14 +5707,14 @@
         <v>50</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J51" s="1"/>
       <c r="K51" s="1">
         <v>45.1</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-43.734999999999999</v>
       </c>
       <c r="M51" s="1"/>
@@ -5686,16 +5730,16 @@
         <v>0</v>
       </c>
       <c r="S51" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0.27300000000000002</v>
       </c>
       <c r="T51" s="5"/>
       <c r="U51" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>519.84102564102545</v>
       </c>
       <c r="V51" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>519.84102564102545</v>
       </c>
       <c r="W51" s="1">
@@ -5706,7 +5750,7 @@
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA51" s="1"/>
@@ -5735,10 +5779,10 @@
     </row>
     <row r="52" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C52" s="1">
         <v>10.574</v>
@@ -5759,14 +5803,14 @@
         <v>50</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1">
         <v>131.1</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-39.091999999999999</v>
       </c>
       <c r="M52" s="1"/>
@@ -5782,19 +5826,19 @@
         <v>54.752200000000023</v>
       </c>
       <c r="S52" s="1">
+        <f t="shared" si="10"/>
+        <v>18.401599999999998</v>
+      </c>
+      <c r="T52" s="5">
+        <f t="shared" si="13"/>
+        <v>112.13199999999995</v>
+      </c>
+      <c r="U52" s="1">
+        <f t="shared" si="11"/>
+        <v>12</v>
+      </c>
+      <c r="V52" s="1">
         <f t="shared" si="12"/>
-        <v>18.401599999999998</v>
-      </c>
-      <c r="T52" s="5">
-        <f t="shared" si="15"/>
-        <v>112.13199999999995</v>
-      </c>
-      <c r="U52" s="1">
-        <f t="shared" si="13"/>
-        <v>12</v>
-      </c>
-      <c r="V52" s="1">
-        <f t="shared" si="14"/>
         <v>5.9063994435266514</v>
       </c>
       <c r="W52" s="1">
@@ -5804,11 +5848,11 @@
         <v>3.7355999999999998</v>
       </c>
       <c r="Y52" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z52" s="1">
-        <f t="shared" si="10"/>
-        <v>112.13199999999995</v>
+        <f t="shared" si="5"/>
+        <v>112</v>
       </c>
       <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
@@ -5836,10 +5880,10 @@
     </row>
     <row r="53" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1">
@@ -5858,14 +5902,14 @@
         <v>45</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1">
         <v>11.7</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>2.109</v>
       </c>
       <c r="M53" s="1"/>
@@ -5881,16 +5925,16 @@
         <v>0</v>
       </c>
       <c r="S53" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>2.7618</v>
       </c>
       <c r="T53" s="5"/>
       <c r="U53" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>50.276269099862411</v>
       </c>
       <c r="V53" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>50.276269099862411</v>
       </c>
       <c r="W53" s="1">
@@ -5901,7 +5945,7 @@
       </c>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA53" s="1"/>
@@ -5930,10 +5974,10 @@
     </row>
     <row r="54" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C54" s="1">
         <v>207</v>
@@ -5954,14 +5998,14 @@
         <v>50</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J54" s="1"/>
       <c r="K54" s="1">
         <v>85</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-5</v>
       </c>
       <c r="M54" s="1"/>
@@ -5977,16 +6021,16 @@
         <v>0</v>
       </c>
       <c r="S54" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>16</v>
       </c>
       <c r="T54" s="5"/>
       <c r="U54" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>12.9375</v>
       </c>
       <c r="V54" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>12.9375</v>
       </c>
       <c r="W54" s="1">
@@ -5997,7 +6041,7 @@
       </c>
       <c r="Y54" s="1"/>
       <c r="Z54" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA54" s="1"/>
@@ -6026,10 +6070,10 @@
     </row>
     <row r="55" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C55" s="1">
         <v>271</v>
@@ -6050,14 +6094,14 @@
         <v>50</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J55" s="1"/>
       <c r="K55" s="1">
         <v>150</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-20</v>
       </c>
       <c r="M55" s="1"/>
@@ -6073,19 +6117,19 @@
         <v>47.111627906976743</v>
       </c>
       <c r="S55" s="1">
+        <f t="shared" si="10"/>
+        <v>26</v>
+      </c>
+      <c r="T55" s="5">
+        <f t="shared" si="13"/>
+        <v>81.19999999999996</v>
+      </c>
+      <c r="U55" s="1">
+        <f t="shared" si="11"/>
+        <v>12</v>
+      </c>
+      <c r="V55" s="1">
         <f t="shared" si="12"/>
-        <v>26</v>
-      </c>
-      <c r="T55" s="5">
-        <f t="shared" si="15"/>
-        <v>81.19999999999996</v>
-      </c>
-      <c r="U55" s="1">
-        <f t="shared" si="13"/>
-        <v>12</v>
-      </c>
-      <c r="V55" s="1">
-        <f t="shared" si="14"/>
         <v>8.8769230769230774</v>
       </c>
       <c r="W55" s="1">
@@ -6096,8 +6140,8 @@
       </c>
       <c r="Y55" s="1"/>
       <c r="Z55" s="1">
-        <f t="shared" si="10"/>
-        <v>36.539999999999985</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
       <c r="AA55" s="1"/>
       <c r="AB55" s="1"/>
@@ -6125,10 +6169,10 @@
     </row>
     <row r="56" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -6141,14 +6185,14 @@
         <v>40</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J56" s="1"/>
       <c r="K56" s="1">
         <v>6</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-6</v>
       </c>
       <c r="M56" s="1"/>
@@ -6164,16 +6208,16 @@
         <v>5</v>
       </c>
       <c r="S56" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="T56" s="5"/>
       <c r="U56" s="1" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V56" s="1" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W56" s="1">
@@ -6184,7 +6228,7 @@
       </c>
       <c r="Y56" s="1"/>
       <c r="Z56" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA56" s="1"/>
@@ -6213,10 +6257,10 @@
     </row>
     <row r="57" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -6229,14 +6273,14 @@
         <v>40</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J57" s="1"/>
       <c r="K57" s="1">
         <v>8</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-8</v>
       </c>
       <c r="M57" s="1"/>
@@ -6252,16 +6296,16 @@
         <v>5</v>
       </c>
       <c r="S57" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="T57" s="5"/>
       <c r="U57" s="1" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V57" s="1" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W57" s="1">
@@ -6272,7 +6316,7 @@
       </c>
       <c r="Y57" s="1"/>
       <c r="Z57" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA57" s="1"/>
@@ -6301,10 +6345,10 @@
     </row>
     <row r="58" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A58" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C58" s="1">
         <v>4.0590000000000002</v>
@@ -6325,14 +6369,14 @@
         <v>50</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J58" s="1"/>
       <c r="K58" s="1">
         <v>77.7</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-30.129000000000005</v>
       </c>
       <c r="M58" s="1"/>
@@ -6348,18 +6392,18 @@
         <v>0</v>
       </c>
       <c r="S58" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>9.5141999999999989</v>
       </c>
       <c r="T58" s="5">
         <v>10</v>
       </c>
       <c r="U58" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>12.530848626263902</v>
       </c>
       <c r="V58" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>11.479788106199157</v>
       </c>
       <c r="W58" s="1">
@@ -6369,10 +6413,10 @@
         <v>7.0168000000000008</v>
       </c>
       <c r="Y58" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z58" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="AA58" s="1"/>
@@ -6401,10 +6445,10 @@
     </row>
     <row r="59" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A59" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C59" s="1">
         <v>175</v>
@@ -6427,14 +6471,14 @@
         <v>731</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J59" s="1"/>
       <c r="K59" s="1">
         <v>39</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>22</v>
       </c>
       <c r="M59" s="1"/>
@@ -6450,16 +6494,16 @@
         <v>0</v>
       </c>
       <c r="S59" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>12.2</v>
       </c>
       <c r="T59" s="5"/>
       <c r="U59" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>12.793028472821398</v>
       </c>
       <c r="V59" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>12.793028472821398</v>
       </c>
       <c r="W59" s="1">
@@ -6469,10 +6513,10 @@
         <v>5.8</v>
       </c>
       <c r="Y59" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z59" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA59" s="1"/>
@@ -6501,10 +6545,10 @@
     </row>
     <row r="60" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A60" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C60" s="1">
         <v>-3.9390000000000001</v>
@@ -6525,14 +6569,14 @@
         <v>50</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J60" s="1"/>
       <c r="K60" s="1">
         <v>138.9</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-79.722000000000008</v>
       </c>
       <c r="M60" s="1"/>
@@ -6548,16 +6592,16 @@
         <v>0</v>
       </c>
       <c r="S60" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>11.835599999999999</v>
       </c>
       <c r="T60" s="5"/>
       <c r="U60" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>15.342580828696564</v>
       </c>
       <c r="V60" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>15.342580828696564</v>
       </c>
       <c r="W60" s="1">
@@ -6567,10 +6611,10 @@
         <v>12.861000000000001</v>
       </c>
       <c r="Y60" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z60" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA60" s="1"/>
@@ -6599,10 +6643,10 @@
     </row>
     <row r="61" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A61" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
@@ -6615,14 +6659,14 @@
         <v>55</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J61" s="1"/>
       <c r="K61" s="1">
         <v>9</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-9</v>
       </c>
       <c r="M61" s="1"/>
@@ -6638,16 +6682,16 @@
         <v>10</v>
       </c>
       <c r="S61" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="T61" s="5"/>
       <c r="U61" s="1" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V61" s="1" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W61" s="1">
@@ -6658,7 +6702,7 @@
       </c>
       <c r="Y61" s="1"/>
       <c r="Z61" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA61" s="1"/>
@@ -6687,10 +6731,10 @@
     </row>
     <row r="62" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A62" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C62" s="1">
         <v>213</v>
@@ -6711,14 +6755,14 @@
         <v>731</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J62" s="1"/>
       <c r="K62" s="1">
         <v>28</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
       <c r="M62" s="1"/>
@@ -6734,16 +6778,16 @@
         <v>0</v>
       </c>
       <c r="S62" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>6.6</v>
       </c>
       <c r="T62" s="5"/>
       <c r="U62" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>30.959397511460384</v>
       </c>
       <c r="V62" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>30.959397511460384</v>
       </c>
       <c r="W62" s="1">
@@ -6753,10 +6797,10 @@
         <v>3.2</v>
       </c>
       <c r="Y62" s="15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Z62" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA62" s="1"/>
@@ -6785,10 +6829,10 @@
     </row>
     <row r="63" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A63" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1">
@@ -6807,14 +6851,14 @@
         <v>50</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J63" s="1"/>
       <c r="K63" s="1">
         <v>11</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-6</v>
       </c>
       <c r="M63" s="1"/>
@@ -6830,18 +6874,18 @@
         <v>0</v>
       </c>
       <c r="S63" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="T63" s="5">
         <v>6</v>
       </c>
       <c r="U63" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>18</v>
       </c>
       <c r="V63" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>12</v>
       </c>
       <c r="W63" s="1">
@@ -6852,8 +6896,8 @@
       </c>
       <c r="Y63" s="1"/>
       <c r="Z63" s="1">
-        <f t="shared" si="10"/>
-        <v>2.4000000000000004</v>
+        <f t="shared" si="5"/>
+        <v>2</v>
       </c>
       <c r="AA63" s="1"/>
       <c r="AB63" s="1"/>
@@ -6881,10 +6925,10 @@
     </row>
     <row r="64" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C64" s="1">
         <v>1.2E-2</v>
@@ -6903,14 +6947,14 @@
         <v>40</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J64" s="1"/>
       <c r="K64" s="1">
         <v>53</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-53</v>
       </c>
       <c r="M64" s="1"/>
@@ -6926,16 +6970,16 @@
         <v>50</v>
       </c>
       <c r="S64" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="T64" s="5"/>
       <c r="U64" s="1" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V64" s="1" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W64" s="1">
@@ -6946,7 +6990,7 @@
       </c>
       <c r="Y64" s="1"/>
       <c r="Z64" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA64" s="1"/>
@@ -6975,10 +7019,10 @@
     </row>
     <row r="65" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A65" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -6991,14 +7035,14 @@
         <v>40</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J65" s="1"/>
       <c r="K65" s="1">
         <v>2.6</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-2.6</v>
       </c>
       <c r="M65" s="1"/>
@@ -7014,16 +7058,16 @@
         <v>50</v>
       </c>
       <c r="S65" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="T65" s="5"/>
       <c r="U65" s="1" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V65" s="1" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W65" s="1">
@@ -7034,7 +7078,7 @@
       </c>
       <c r="Y65" s="1"/>
       <c r="Z65" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA65" s="1"/>
@@ -7063,10 +7107,10 @@
     </row>
     <row r="66" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A66" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C66" s="1">
         <v>6</v>
@@ -7087,14 +7131,14 @@
         <v>40</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J66" s="1"/>
       <c r="K66" s="1">
         <v>232</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-60</v>
       </c>
       <c r="M66" s="1"/>
@@ -7110,19 +7154,19 @@
         <v>0</v>
       </c>
       <c r="S66" s="1">
+        <f t="shared" si="10"/>
+        <v>34.4</v>
+      </c>
+      <c r="T66" s="5">
+        <f t="shared" si="13"/>
+        <v>115.06491994177577</v>
+      </c>
+      <c r="U66" s="1">
+        <f t="shared" si="11"/>
+        <v>12</v>
+      </c>
+      <c r="V66" s="1">
         <f t="shared" si="12"/>
-        <v>34.4</v>
-      </c>
-      <c r="T66" s="5">
-        <f t="shared" si="15"/>
-        <v>115.06491994177577</v>
-      </c>
-      <c r="U66" s="1">
-        <f t="shared" si="13"/>
-        <v>12</v>
-      </c>
-      <c r="V66" s="1">
-        <f t="shared" si="14"/>
         <v>8.6550895365762841</v>
       </c>
       <c r="W66" s="1">
@@ -7133,8 +7177,8 @@
       </c>
       <c r="Y66" s="1"/>
       <c r="Z66" s="1">
-        <f t="shared" si="10"/>
-        <v>46.025967976710312</v>
+        <f t="shared" si="5"/>
+        <v>46</v>
       </c>
       <c r="AA66" s="1"/>
       <c r="AB66" s="1"/>
@@ -7162,10 +7206,10 @@
     </row>
     <row r="67" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A67" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1">
@@ -7180,14 +7224,14 @@
         <v>40</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J67" s="1"/>
       <c r="K67" s="1">
         <v>38</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-38</v>
       </c>
       <c r="M67" s="1"/>
@@ -7203,16 +7247,16 @@
         <v>100</v>
       </c>
       <c r="S67" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="T67" s="5"/>
       <c r="U67" s="1" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V67" s="1" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W67" s="1">
@@ -7223,7 +7267,7 @@
       </c>
       <c r="Y67" s="1"/>
       <c r="Z67" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA67" s="1"/>
@@ -7252,10 +7296,10 @@
     </row>
     <row r="68" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A68" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C68" s="1">
         <v>6.5410000000000004</v>
@@ -7276,14 +7320,14 @@
         <v>40</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J68" s="1"/>
       <c r="K68" s="1">
         <v>81.3</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-6.2289999999999992</v>
       </c>
       <c r="M68" s="1"/>
@@ -7301,18 +7345,18 @@
         <v>0</v>
       </c>
       <c r="S68" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>15.014199999999999</v>
       </c>
       <c r="T68" s="5">
         <v>100</v>
       </c>
       <c r="U68" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>7.7066712920154314</v>
       </c>
       <c r="V68" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>1.0463097675918858</v>
       </c>
       <c r="W68" s="1">
@@ -7323,7 +7367,7 @@
       </c>
       <c r="Y68" s="1"/>
       <c r="Z68" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="AA68" s="1"/>
@@ -7352,10 +7396,10 @@
     </row>
     <row r="69" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A69" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1">
@@ -7374,14 +7418,14 @@
         <v>40</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J69" s="1"/>
       <c r="K69" s="1">
         <v>75.599999999999994</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>-0.18099999999999739</v>
       </c>
       <c r="M69" s="1"/>
@@ -7399,18 +7443,18 @@
         <v>0</v>
       </c>
       <c r="S69" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>15.0838</v>
       </c>
       <c r="T69" s="5">
         <v>100</v>
       </c>
       <c r="U69" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>7.2327418398729542</v>
       </c>
       <c r="V69" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>0.6031127013269646</v>
       </c>
       <c r="W69" s="1">
@@ -7421,7 +7465,7 @@
       </c>
       <c r="Y69" s="1"/>
       <c r="Z69" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="AA69" s="1"/>
@@ -7450,10 +7494,10 @@
     </row>
     <row r="70" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A70" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C70" s="1">
         <v>5.3769999999999998</v>
@@ -7474,14 +7518,14 @@
         <v>40</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J70" s="1"/>
       <c r="K70" s="1">
         <v>34.200000000000003</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L101" si="16">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="14">E70-K70</f>
         <v>-13.232000000000003</v>
       </c>
       <c r="M70" s="1"/>
@@ -7499,18 +7543,18 @@
         <v>0</v>
       </c>
       <c r="S70" s="1">
-        <f t="shared" ref="S70:S101" si="17">E70/5</f>
+        <f t="shared" ref="S70:S101" si="15">E70/5</f>
         <v>4.1936</v>
       </c>
       <c r="T70" s="5">
         <v>50</v>
       </c>
       <c r="U70" s="1">
-        <f t="shared" ref="U70:U101" si="18">(F70+O70+P70+Q70+R70+T70)/S70</f>
+        <f t="shared" ref="U70:U101" si="16">(F70+O70+P70+Q70+R70+T70)/S70</f>
         <v>52.411647238024692</v>
       </c>
       <c r="V70" s="1">
-        <f t="shared" ref="V70:V101" si="19">(F70+O70+P70+Q70+R70)/S70</f>
+        <f t="shared" ref="V70:V101" si="17">(F70+O70+P70+Q70+R70)/S70</f>
         <v>40.48871705870382</v>
       </c>
       <c r="W70" s="1">
@@ -7521,7 +7565,7 @@
       </c>
       <c r="Y70" s="1"/>
       <c r="Z70" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>50</v>
       </c>
       <c r="AA70" s="1"/>
@@ -7550,10 +7594,10 @@
     </row>
     <row r="71" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A71" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
@@ -7566,14 +7610,14 @@
         <v>40</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J71" s="1"/>
       <c r="K71" s="1">
         <v>7.9</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-7.9</v>
       </c>
       <c r="M71" s="1"/>
@@ -7589,16 +7633,16 @@
         <v>0</v>
       </c>
       <c r="S71" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T71" s="5"/>
       <c r="U71" s="1" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V71" s="1" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W71" s="1">
@@ -7609,7 +7653,7 @@
       </c>
       <c r="Y71" s="1"/>
       <c r="Z71" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="Z71:Z131" si="18">ROUND(G71*T71,0)</f>
         <v>0</v>
       </c>
       <c r="AA71" s="1"/>
@@ -7638,10 +7682,10 @@
     </row>
     <row r="72" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
@@ -7652,12 +7696,12 @@
       </c>
       <c r="H72" s="10"/>
       <c r="I72" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J72" s="10"/>
       <c r="K72" s="10"/>
       <c r="L72" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M72" s="10"/>
@@ -7671,28 +7715,31 @@
         <v>0</v>
       </c>
       <c r="S72" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T72" s="12"/>
       <c r="U72" s="10" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V72" s="10" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W72" s="10">
+        <v>0</v>
+      </c>
+      <c r="X72" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z72" s="1">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V72" s="10" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W72" s="10">
-        <v>0</v>
-      </c>
-      <c r="X72" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y72" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z72" s="10"/>
+        <v>0</v>
+      </c>
       <c r="AA72" s="1"/>
       <c r="AB72" s="1"/>
       <c r="AC72" s="1"/>
@@ -7719,10 +7766,10 @@
     </row>
     <row r="73" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A73" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C73" s="1">
         <v>0.02</v>
@@ -7739,14 +7786,14 @@
         <v>30</v>
       </c>
       <c r="I73" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J73" s="1"/>
       <c r="K73" s="1">
         <v>9.3000000000000007</v>
       </c>
       <c r="L73" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-9.3000000000000007</v>
       </c>
       <c r="M73" s="1"/>
@@ -7762,16 +7809,16 @@
         <v>120</v>
       </c>
       <c r="S73" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T73" s="5"/>
       <c r="U73" s="1" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V73" s="1" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W73" s="1">
@@ -7782,7 +7829,7 @@
       </c>
       <c r="Y73" s="1"/>
       <c r="Z73" s="1">
-        <f t="shared" ref="Z73:Z84" si="20">G73*T73</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA73" s="1"/>
@@ -7811,10 +7858,10 @@
     </row>
     <row r="74" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A74" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C74" s="1">
         <v>102</v>
@@ -7835,14 +7882,14 @@
         <v>60</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J74" s="1"/>
       <c r="K74" s="1">
         <v>44</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-26</v>
       </c>
       <c r="M74" s="1"/>
@@ -7858,16 +7905,16 @@
         <v>0</v>
       </c>
       <c r="S74" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>3.6</v>
       </c>
       <c r="T74" s="5"/>
       <c r="U74" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>88.028368794326241</v>
       </c>
       <c r="V74" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>88.028368794326241</v>
       </c>
       <c r="W74" s="1">
@@ -7877,10 +7924,10 @@
         <v>7</v>
       </c>
       <c r="Y74" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Z74" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA74" s="1"/>
@@ -7909,10 +7956,10 @@
     </row>
     <row r="75" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A75" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C75" s="1">
         <v>114</v>
@@ -7933,14 +7980,14 @@
         <v>60</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J75" s="1"/>
       <c r="K75" s="1">
         <v>63</v>
       </c>
       <c r="L75" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-45</v>
       </c>
       <c r="M75" s="1"/>
@@ -7956,16 +8003,16 @@
         <v>0</v>
       </c>
       <c r="S75" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>3.6</v>
       </c>
       <c r="T75" s="5"/>
       <c r="U75" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>74.795281582952825</v>
       </c>
       <c r="V75" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>74.795281582952825</v>
       </c>
       <c r="W75" s="1">
@@ -7975,10 +8022,10 @@
         <v>10.6</v>
       </c>
       <c r="Y75" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Z75" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA75" s="1"/>
@@ -8007,10 +8054,10 @@
     </row>
     <row r="76" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A76" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1">
@@ -8029,14 +8076,14 @@
         <v>90</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J76" s="1"/>
       <c r="K76" s="1">
         <v>32</v>
       </c>
       <c r="L76" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-1</v>
       </c>
       <c r="M76" s="1"/>
@@ -8052,16 +8099,16 @@
         <v>0</v>
       </c>
       <c r="S76" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>6.2</v>
       </c>
       <c r="T76" s="5"/>
       <c r="U76" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>22.706744868035191</v>
       </c>
       <c r="V76" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>22.706744868035191</v>
       </c>
       <c r="W76" s="1">
@@ -8072,7 +8119,7 @@
       </c>
       <c r="Y76" s="1"/>
       <c r="Z76" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA76" s="1"/>
@@ -8101,10 +8148,10 @@
     </row>
     <row r="77" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A77" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C77" s="1">
         <v>5</v>
@@ -8125,14 +8172,14 @@
         <v>60</v>
       </c>
       <c r="I77" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J77" s="1"/>
       <c r="K77" s="1">
         <v>48</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
       <c r="M77" s="1"/>
@@ -8148,16 +8195,16 @@
         <v>0</v>
       </c>
       <c r="S77" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>10</v>
       </c>
       <c r="T77" s="5"/>
       <c r="U77" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>18.541632653061225</v>
       </c>
       <c r="V77" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>18.541632653061225</v>
       </c>
       <c r="W77" s="1">
@@ -8168,7 +8215,7 @@
       </c>
       <c r="Y77" s="1"/>
       <c r="Z77" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA77" s="1"/>
@@ -8197,10 +8244,10 @@
     </row>
     <row r="78" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A78" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1">
@@ -8219,14 +8266,14 @@
         <v>90</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J78" s="1"/>
       <c r="K78" s="1">
         <v>55</v>
       </c>
       <c r="L78" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-9</v>
       </c>
       <c r="M78" s="1"/>
@@ -8242,16 +8289,16 @@
         <v>0</v>
       </c>
       <c r="S78" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>9.1999999999999993</v>
       </c>
       <c r="T78" s="5"/>
       <c r="U78" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>23.786145204909509</v>
       </c>
       <c r="V78" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>23.786145204909509</v>
       </c>
       <c r="W78" s="1">
@@ -8262,7 +8309,7 @@
       </c>
       <c r="Y78" s="1"/>
       <c r="Z78" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA78" s="1"/>
@@ -8291,10 +8338,10 @@
     </row>
     <row r="79" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A79" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1">
@@ -8311,14 +8358,14 @@
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J79" s="1"/>
       <c r="K79" s="1">
         <v>13</v>
       </c>
       <c r="L79" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-12</v>
       </c>
       <c r="M79" s="1"/>
@@ -8334,16 +8381,16 @@
         <v>0</v>
       </c>
       <c r="S79" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0.2</v>
       </c>
       <c r="T79" s="5"/>
       <c r="U79" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>145</v>
       </c>
       <c r="V79" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>145</v>
       </c>
       <c r="W79" s="1">
@@ -8354,7 +8401,7 @@
       </c>
       <c r="Y79" s="1"/>
       <c r="Z79" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA79" s="1"/>
@@ -8383,10 +8430,10 @@
     </row>
     <row r="80" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A80" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C80" s="1">
         <v>120.2</v>
@@ -8407,14 +8454,14 @@
         <v>70</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J80" s="1"/>
       <c r="K80" s="1">
         <v>69</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-48</v>
       </c>
       <c r="M80" s="1"/>
@@ -8430,16 +8477,16 @@
         <v>0</v>
       </c>
       <c r="S80" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>4.2</v>
       </c>
       <c r="T80" s="5"/>
       <c r="U80" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>59.166199813258636</v>
       </c>
       <c r="V80" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>59.166199813258636</v>
       </c>
       <c r="W80" s="1">
@@ -8449,10 +8496,10 @@
         <v>7.6</v>
       </c>
       <c r="Y80" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Z80" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA80" s="1"/>
@@ -8481,10 +8528,10 @@
     </row>
     <row r="81" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A81" s="16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1">
@@ -8503,14 +8550,14 @@
         <v>40</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J81" s="1"/>
       <c r="K81" s="1">
         <v>30</v>
       </c>
       <c r="L81" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-12</v>
       </c>
       <c r="M81" s="1"/>
@@ -8526,19 +8573,19 @@
         <v>0</v>
       </c>
       <c r="S81" s="1">
+        <f t="shared" si="15"/>
+        <v>3.6</v>
+      </c>
+      <c r="T81" s="5">
+        <f t="shared" ref="T81" si="19">12*S81-R81-Q81-P81-O81-F81</f>
+        <v>10.981659388646293</v>
+      </c>
+      <c r="U81" s="1">
+        <f t="shared" si="16"/>
+        <v>12</v>
+      </c>
+      <c r="V81" s="1">
         <f t="shared" si="17"/>
-        <v>3.6</v>
-      </c>
-      <c r="T81" s="5">
-        <f t="shared" ref="T73:T84" si="21">12*S81-R81-Q81-P81-O81-F81</f>
-        <v>10.981659388646293</v>
-      </c>
-      <c r="U81" s="1">
-        <f t="shared" si="18"/>
-        <v>12</v>
-      </c>
-      <c r="V81" s="1">
-        <f t="shared" si="19"/>
         <v>8.9495390587093642</v>
       </c>
       <c r="W81" s="1">
@@ -8549,8 +8596,8 @@
       </c>
       <c r="Y81" s="1"/>
       <c r="Z81" s="1">
-        <f t="shared" si="20"/>
-        <v>3.6239475982532765</v>
+        <f t="shared" si="18"/>
+        <v>4</v>
       </c>
       <c r="AA81" s="1"/>
       <c r="AB81" s="1"/>
@@ -8578,10 +8625,10 @@
     </row>
     <row r="82" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A82" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C82" s="1">
         <v>23</v>
@@ -8602,14 +8649,14 @@
         <v>55</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J82" s="1"/>
       <c r="K82" s="1">
         <v>13</v>
       </c>
       <c r="L82" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-3</v>
       </c>
       <c r="M82" s="1"/>
@@ -8625,16 +8672,16 @@
         <v>0</v>
       </c>
       <c r="S82" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
       <c r="T82" s="5"/>
       <c r="U82" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>21.5</v>
       </c>
       <c r="V82" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>21.5</v>
       </c>
       <c r="W82" s="1">
@@ -8644,10 +8691,10 @@
         <v>0.6</v>
       </c>
       <c r="Y82" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Z82" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA82" s="1"/>
@@ -8676,10 +8723,10 @@
     </row>
     <row r="83" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A83" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C83" s="1">
         <v>-2</v>
@@ -8700,14 +8747,14 @@
         <v>40</v>
       </c>
       <c r="I83" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J83" s="1"/>
       <c r="K83" s="1">
         <v>1</v>
       </c>
       <c r="L83" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M83" s="1"/>
@@ -8723,16 +8770,16 @@
         <v>0</v>
       </c>
       <c r="S83" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0.2</v>
       </c>
       <c r="T83" s="5"/>
       <c r="U83" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>165</v>
       </c>
       <c r="V83" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>165</v>
       </c>
       <c r="W83" s="1">
@@ -8743,7 +8790,7 @@
       </c>
       <c r="Y83" s="1"/>
       <c r="Z83" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA83" s="1"/>
@@ -8772,10 +8819,10 @@
     </row>
     <row r="84" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A84" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1">
@@ -8794,14 +8841,14 @@
         <v>45</v>
       </c>
       <c r="I84" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J84" s="1"/>
       <c r="K84" s="1">
         <v>15</v>
       </c>
       <c r="L84" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-4</v>
       </c>
       <c r="M84" s="1"/>
@@ -8817,16 +8864,16 @@
         <v>0</v>
       </c>
       <c r="S84" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="T84" s="5"/>
       <c r="U84" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>16.932310114128295</v>
       </c>
       <c r="V84" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>16.932310114128295</v>
       </c>
       <c r="W84" s="1">
@@ -8837,7 +8884,7 @@
       </c>
       <c r="Y84" s="1"/>
       <c r="Z84" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA84" s="1"/>
@@ -8866,10 +8913,10 @@
     </row>
     <row r="85" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A85" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="10"/>
@@ -8880,12 +8927,12 @@
       </c>
       <c r="H85" s="10"/>
       <c r="I85" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J85" s="10"/>
       <c r="K85" s="10"/>
       <c r="L85" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M85" s="10"/>
@@ -8899,28 +8946,31 @@
         <v>0</v>
       </c>
       <c r="S85" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T85" s="12"/>
       <c r="U85" s="10" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V85" s="10" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W85" s="10">
+        <v>0</v>
+      </c>
+      <c r="X85" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z85" s="1">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V85" s="10" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W85" s="10">
-        <v>0</v>
-      </c>
-      <c r="X85" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y85" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z85" s="10"/>
+        <v>0</v>
+      </c>
       <c r="AA85" s="1"/>
       <c r="AB85" s="1"/>
       <c r="AC85" s="1"/>
@@ -8947,10 +8997,10 @@
     </row>
     <row r="86" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
@@ -8961,12 +9011,12 @@
       </c>
       <c r="H86" s="10"/>
       <c r="I86" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J86" s="10"/>
       <c r="K86" s="10"/>
       <c r="L86" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M86" s="10"/>
@@ -8980,28 +9030,31 @@
         <v>0</v>
       </c>
       <c r="S86" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T86" s="12"/>
       <c r="U86" s="10" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V86" s="10" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W86" s="10">
+        <v>0</v>
+      </c>
+      <c r="X86" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z86" s="1">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V86" s="10" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W86" s="10">
-        <v>0</v>
-      </c>
-      <c r="X86" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y86" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z86" s="10"/>
+        <v>0</v>
+      </c>
       <c r="AA86" s="1"/>
       <c r="AB86" s="1"/>
       <c r="AC86" s="1"/>
@@ -9028,10 +9081,10 @@
     </row>
     <row r="87" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
@@ -9042,12 +9095,12 @@
       </c>
       <c r="H87" s="10"/>
       <c r="I87" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J87" s="10"/>
       <c r="K87" s="10"/>
       <c r="L87" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M87" s="10"/>
@@ -9061,28 +9114,31 @@
         <v>0</v>
       </c>
       <c r="S87" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T87" s="12"/>
       <c r="U87" s="10" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V87" s="10" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W87" s="10">
+        <v>0</v>
+      </c>
+      <c r="X87" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z87" s="1">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V87" s="10" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W87" s="10">
-        <v>0</v>
-      </c>
-      <c r="X87" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y87" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z87" s="10"/>
+        <v>0</v>
+      </c>
       <c r="AA87" s="1"/>
       <c r="AB87" s="1"/>
       <c r="AC87" s="1"/>
@@ -9109,10 +9165,10 @@
     </row>
     <row r="88" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A88" s="16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C88" s="1">
         <v>1.91</v>
@@ -9133,14 +9189,14 @@
         <v>60</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J88" s="1"/>
       <c r="K88" s="1">
         <v>89.9</v>
       </c>
       <c r="L88" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-77.800000000000011</v>
       </c>
       <c r="M88" s="1"/>
@@ -9156,16 +9212,16 @@
         <v>0</v>
       </c>
       <c r="S88" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>2.42</v>
       </c>
       <c r="T88" s="5"/>
       <c r="U88" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>111.78181818181818</v>
       </c>
       <c r="V88" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>111.78181818181818</v>
       </c>
       <c r="W88" s="1">
@@ -9176,7 +9232,7 @@
       </c>
       <c r="Y88" s="1"/>
       <c r="Z88" s="1">
-        <f>G88*T88</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA88" s="1"/>
@@ -9205,10 +9261,10 @@
     </row>
     <row r="89" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="10"/>
@@ -9219,12 +9275,12 @@
       </c>
       <c r="H89" s="10"/>
       <c r="I89" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J89" s="10"/>
       <c r="K89" s="10"/>
       <c r="L89" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M89" s="10"/>
@@ -9238,28 +9294,31 @@
         <v>0</v>
       </c>
       <c r="S89" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T89" s="12"/>
       <c r="U89" s="10" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V89" s="10" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W89" s="10">
+        <v>0</v>
+      </c>
+      <c r="X89" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z89" s="1">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V89" s="10" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W89" s="10">
-        <v>0</v>
-      </c>
-      <c r="X89" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y89" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z89" s="10"/>
+        <v>0</v>
+      </c>
       <c r="AA89" s="1"/>
       <c r="AB89" s="1"/>
       <c r="AC89" s="1"/>
@@ -9286,10 +9345,10 @@
     </row>
     <row r="90" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A90" s="16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C90" s="1">
         <v>722.94200000000001</v>
@@ -9310,14 +9369,14 @@
         <v>60</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J90" s="1"/>
       <c r="K90" s="1">
         <v>567.5</v>
       </c>
       <c r="L90" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-9.68100000000004</v>
       </c>
       <c r="M90" s="1"/>
@@ -9333,19 +9392,19 @@
         <v>0</v>
       </c>
       <c r="S90" s="1">
+        <f t="shared" si="15"/>
+        <v>111.56379999999999</v>
+      </c>
+      <c r="T90" s="5">
+        <f t="shared" ref="T90:T92" si="20">12*S90-R90-Q90-P90-O90-F90</f>
+        <v>27.225830600724521</v>
+      </c>
+      <c r="U90" s="1">
+        <f t="shared" si="16"/>
+        <v>11.999999999999998</v>
+      </c>
+      <c r="V90" s="1">
         <f t="shared" si="17"/>
-        <v>111.56379999999999</v>
-      </c>
-      <c r="T90" s="5">
-        <f t="shared" ref="T90:T92" si="22">12*S90-R90-Q90-P90-O90-F90</f>
-        <v>27.225830600724521</v>
-      </c>
-      <c r="U90" s="1">
-        <f t="shared" si="18"/>
-        <v>11.999999999999998</v>
-      </c>
-      <c r="V90" s="1">
-        <f t="shared" si="19"/>
         <v>11.755961785088671</v>
       </c>
       <c r="W90" s="1">
@@ -9356,8 +9415,8 @@
       </c>
       <c r="Y90" s="1"/>
       <c r="Z90" s="1">
-        <f>G90*T90</f>
-        <v>27.225830600724521</v>
+        <f t="shared" si="18"/>
+        <v>27</v>
       </c>
       <c r="AA90" s="1"/>
       <c r="AB90" s="1"/>
@@ -9385,10 +9444,10 @@
     </row>
     <row r="91" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A91" s="16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C91" s="1">
         <v>75.394000000000005</v>
@@ -9409,14 +9468,14 @@
         <v>60</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J91" s="1"/>
       <c r="K91" s="1">
         <v>598.5</v>
       </c>
       <c r="L91" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-103.83800000000002</v>
       </c>
       <c r="M91" s="1"/>
@@ -9432,19 +9491,19 @@
         <v>0</v>
       </c>
       <c r="S91" s="1">
+        <f t="shared" si="15"/>
+        <v>98.932400000000001</v>
+      </c>
+      <c r="T91" s="5">
+        <f t="shared" si="20"/>
+        <v>479.92177665822271</v>
+      </c>
+      <c r="U91" s="1">
+        <f t="shared" si="16"/>
+        <v>11.999999999999998</v>
+      </c>
+      <c r="V91" s="1">
         <f t="shared" si="17"/>
-        <v>98.932400000000001</v>
-      </c>
-      <c r="T91" s="5">
-        <f t="shared" si="22"/>
-        <v>479.92177665822271</v>
-      </c>
-      <c r="U91" s="1">
-        <f t="shared" si="18"/>
-        <v>11.999999999999998</v>
-      </c>
-      <c r="V91" s="1">
-        <f t="shared" si="19"/>
         <v>7.1489928814198098</v>
       </c>
       <c r="W91" s="1">
@@ -9455,8 +9514,8 @@
       </c>
       <c r="Y91" s="1"/>
       <c r="Z91" s="1">
-        <f>G91*T91</f>
-        <v>479.92177665822271</v>
+        <f t="shared" si="18"/>
+        <v>480</v>
       </c>
       <c r="AA91" s="1"/>
       <c r="AB91" s="1"/>
@@ -9484,10 +9543,10 @@
     </row>
     <row r="92" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A92" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C92" s="1">
         <v>27.984999999999999</v>
@@ -9510,14 +9569,14 @@
         <v>60</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J92" s="1"/>
       <c r="K92" s="1">
         <v>759</v>
       </c>
       <c r="L92" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-78.182999999999993</v>
       </c>
       <c r="M92" s="1"/>
@@ -9533,19 +9592,19 @@
         <v>251.10125231080929</v>
       </c>
       <c r="S92" s="1">
+        <f t="shared" si="15"/>
+        <v>136.1634</v>
+      </c>
+      <c r="T92" s="5">
+        <f t="shared" si="20"/>
+        <v>234.9879999999996</v>
+      </c>
+      <c r="U92" s="1">
+        <f t="shared" si="16"/>
+        <v>12</v>
+      </c>
+      <c r="V92" s="1">
         <f t="shared" si="17"/>
-        <v>136.1634</v>
-      </c>
-      <c r="T92" s="5">
-        <f t="shared" si="22"/>
-        <v>234.9879999999996</v>
-      </c>
-      <c r="U92" s="1">
-        <f t="shared" si="18"/>
-        <v>12</v>
-      </c>
-      <c r="V92" s="1">
-        <f t="shared" si="19"/>
         <v>10.274220532095999</v>
       </c>
       <c r="W92" s="1">
@@ -9556,8 +9615,8 @@
       </c>
       <c r="Y92" s="1"/>
       <c r="Z92" s="1">
-        <f>G92*T92</f>
-        <v>234.9879999999996</v>
+        <f t="shared" si="18"/>
+        <v>235</v>
       </c>
       <c r="AA92" s="1"/>
       <c r="AB92" s="1"/>
@@ -9585,10 +9644,10 @@
     </row>
     <row r="93" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A93" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="10"/>
@@ -9599,12 +9658,12 @@
       </c>
       <c r="H93" s="10"/>
       <c r="I93" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J93" s="10"/>
       <c r="K93" s="10"/>
       <c r="L93" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M93" s="10"/>
@@ -9618,28 +9677,31 @@
         <v>0</v>
       </c>
       <c r="S93" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T93" s="12"/>
       <c r="U93" s="10" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V93" s="10" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W93" s="10">
+        <v>0</v>
+      </c>
+      <c r="X93" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z93" s="1">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V93" s="10" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W93" s="10">
-        <v>0</v>
-      </c>
-      <c r="X93" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y93" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z93" s="10"/>
+        <v>0</v>
+      </c>
       <c r="AA93" s="1"/>
       <c r="AB93" s="1"/>
       <c r="AC93" s="1"/>
@@ -9666,10 +9728,10 @@
     </row>
     <row r="94" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A94" s="16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
@@ -9682,14 +9744,14 @@
         <v>40</v>
       </c>
       <c r="I94" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J94" s="1"/>
       <c r="K94" s="1">
         <v>6</v>
       </c>
       <c r="L94" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-6</v>
       </c>
       <c r="M94" s="1"/>
@@ -9705,16 +9767,16 @@
         <v>100</v>
       </c>
       <c r="S94" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T94" s="5"/>
       <c r="U94" s="1" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V94" s="1" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W94" s="1">
@@ -9725,7 +9787,7 @@
       </c>
       <c r="Y94" s="1"/>
       <c r="Z94" s="1">
-        <f>G94*T94</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA94" s="1"/>
@@ -9754,10 +9816,10 @@
     </row>
     <row r="95" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A95" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="10"/>
@@ -9768,12 +9830,12 @@
       </c>
       <c r="H95" s="10"/>
       <c r="I95" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J95" s="10"/>
       <c r="K95" s="10"/>
       <c r="L95" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M95" s="10"/>
@@ -9787,28 +9849,31 @@
         <v>0</v>
       </c>
       <c r="S95" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T95" s="12"/>
       <c r="U95" s="10" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V95" s="10" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W95" s="10">
+        <v>0</v>
+      </c>
+      <c r="X95" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y95" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z95" s="1">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V95" s="10" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W95" s="10">
-        <v>0</v>
-      </c>
-      <c r="X95" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y95" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z95" s="10"/>
+        <v>0</v>
+      </c>
       <c r="AA95" s="1"/>
       <c r="AB95" s="1"/>
       <c r="AC95" s="1"/>
@@ -9835,10 +9900,10 @@
     </row>
     <row r="96" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A96" s="16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="1">
@@ -9857,14 +9922,14 @@
         <v>90</v>
       </c>
       <c r="I96" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J96" s="1"/>
       <c r="K96" s="1">
         <v>11</v>
       </c>
       <c r="L96" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-1</v>
       </c>
       <c r="M96" s="1"/>
@@ -9880,16 +9945,16 @@
         <v>50</v>
       </c>
       <c r="S96" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
       <c r="T96" s="5"/>
       <c r="U96" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>35.671875</v>
       </c>
       <c r="V96" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>35.671875</v>
       </c>
       <c r="W96" s="1">
@@ -9900,7 +9965,7 @@
       </c>
       <c r="Y96" s="1"/>
       <c r="Z96" s="1">
-        <f t="shared" ref="Z96:Z101" si="23">G96*T96</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA96" s="1"/>
@@ -9929,10 +9994,10 @@
     </row>
     <row r="97" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A97" s="16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
@@ -9949,14 +10014,14 @@
         <v>90</v>
       </c>
       <c r="I97" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J97" s="1"/>
       <c r="K97" s="1">
         <v>9</v>
       </c>
       <c r="L97" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-6</v>
       </c>
       <c r="M97" s="1"/>
@@ -9974,18 +10039,18 @@
         <v>40</v>
       </c>
       <c r="S97" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0.6</v>
       </c>
       <c r="T97" s="5">
         <v>10</v>
       </c>
       <c r="U97" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>111.65559246954597</v>
       </c>
       <c r="V97" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>94.988925802879294</v>
       </c>
       <c r="W97" s="1">
@@ -9996,8 +10061,8 @@
       </c>
       <c r="Y97" s="1"/>
       <c r="Z97" s="1">
-        <f t="shared" si="23"/>
-        <v>0.70000000000000007</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="AA97" s="1"/>
       <c r="AB97" s="1"/>
@@ -10025,10 +10090,10 @@
     </row>
     <row r="98" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A98" s="16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="1">
@@ -10047,14 +10112,14 @@
         <v>90</v>
       </c>
       <c r="I98" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J98" s="1"/>
       <c r="K98" s="1">
         <v>31</v>
       </c>
       <c r="L98" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-12</v>
       </c>
       <c r="M98" s="1"/>
@@ -10070,18 +10135,18 @@
         <v>0</v>
       </c>
       <c r="S98" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>3.8</v>
       </c>
       <c r="T98" s="5">
         <v>10</v>
       </c>
       <c r="U98" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>19.54765947125879</v>
       </c>
       <c r="V98" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>16.916080523890368</v>
       </c>
       <c r="W98" s="1">
@@ -10092,8 +10157,8 @@
       </c>
       <c r="Y98" s="1"/>
       <c r="Z98" s="1">
-        <f t="shared" si="23"/>
-        <v>0.70000000000000007</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="AA98" s="1"/>
       <c r="AB98" s="1"/>
@@ -10121,10 +10186,10 @@
     </row>
     <row r="99" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A99" s="16" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C99" s="1">
         <v>60</v>
@@ -10143,14 +10208,14 @@
       </c>
       <c r="H99" s="1"/>
       <c r="I99" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J99" s="1"/>
       <c r="K99" s="1">
         <v>35</v>
       </c>
       <c r="L99" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-5</v>
       </c>
       <c r="M99" s="1"/>
@@ -10166,19 +10231,19 @@
         <v>20</v>
       </c>
       <c r="S99" s="1">
+        <f t="shared" si="15"/>
+        <v>6</v>
+      </c>
+      <c r="T99" s="5">
+        <f t="shared" ref="T99:T100" si="21">12*S99-R99-Q99-P99-O99-F99</f>
+        <v>20</v>
+      </c>
+      <c r="U99" s="1">
+        <f t="shared" si="16"/>
+        <v>12</v>
+      </c>
+      <c r="V99" s="1">
         <f t="shared" si="17"/>
-        <v>6</v>
-      </c>
-      <c r="T99" s="5">
-        <f t="shared" ref="T96:T101" si="24">12*S99-R99-Q99-P99-O99-F99</f>
-        <v>20</v>
-      </c>
-      <c r="U99" s="1">
-        <f t="shared" si="18"/>
-        <v>12</v>
-      </c>
-      <c r="V99" s="1">
-        <f t="shared" si="19"/>
         <v>8.6666666666666661</v>
       </c>
       <c r="W99" s="1">
@@ -10189,7 +10254,7 @@
       </c>
       <c r="Y99" s="1"/>
       <c r="Z99" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="18"/>
         <v>6</v>
       </c>
       <c r="AA99" s="1"/>
@@ -10218,10 +10283,10 @@
     </row>
     <row r="100" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A100" s="16" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C100" s="1">
         <v>22.241</v>
@@ -10242,14 +10307,14 @@
         <v>55</v>
       </c>
       <c r="I100" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J100" s="1"/>
       <c r="K100" s="1">
         <v>21.9</v>
       </c>
       <c r="L100" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-5.3719999999999999</v>
       </c>
       <c r="M100" s="1"/>
@@ -10265,19 +10330,19 @@
         <v>0</v>
       </c>
       <c r="S100" s="1">
+        <f t="shared" si="15"/>
+        <v>3.3055999999999996</v>
+      </c>
+      <c r="T100" s="5">
+        <f t="shared" si="21"/>
+        <v>20.954199999999993</v>
+      </c>
+      <c r="U100" s="1">
+        <f t="shared" si="16"/>
+        <v>12</v>
+      </c>
+      <c r="V100" s="1">
         <f t="shared" si="17"/>
-        <v>3.3055999999999996</v>
-      </c>
-      <c r="T100" s="5">
-        <f t="shared" si="24"/>
-        <v>20.954199999999993</v>
-      </c>
-      <c r="U100" s="1">
-        <f t="shared" si="18"/>
-        <v>12</v>
-      </c>
-      <c r="V100" s="1">
-        <f t="shared" si="19"/>
         <v>5.660999515972895</v>
       </c>
       <c r="W100" s="1">
@@ -10288,8 +10353,8 @@
       </c>
       <c r="Y100" s="1"/>
       <c r="Z100" s="1">
-        <f t="shared" si="23"/>
-        <v>20.954199999999993</v>
+        <f t="shared" si="18"/>
+        <v>21</v>
       </c>
       <c r="AA100" s="1"/>
       <c r="AB100" s="1"/>
@@ -10317,10 +10382,10 @@
     </row>
     <row r="101" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A101" s="16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C101" s="1">
         <v>106</v>
@@ -10339,14 +10404,14 @@
         <v>30</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J101" s="1"/>
       <c r="K101" s="1">
         <v>42</v>
       </c>
       <c r="L101" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-22</v>
       </c>
       <c r="M101" s="1"/>
@@ -10362,16 +10427,16 @@
         <v>0</v>
       </c>
       <c r="S101" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>4</v>
       </c>
       <c r="T101" s="5"/>
       <c r="U101" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>18.75</v>
       </c>
       <c r="V101" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>18.75</v>
       </c>
       <c r="W101" s="1">
@@ -10381,10 +10446,10 @@
         <v>2</v>
       </c>
       <c r="Y101" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Z101" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA101" s="1"/>
@@ -10413,10 +10478,10 @@
     </row>
     <row r="102" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A102" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C102" s="10"/>
       <c r="D102" s="10"/>
@@ -10427,12 +10492,12 @@
       </c>
       <c r="H102" s="10"/>
       <c r="I102" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J102" s="10"/>
       <c r="K102" s="10"/>
       <c r="L102" s="10">
-        <f t="shared" ref="L102:L133" si="25">E102-K102</f>
+        <f t="shared" ref="L102:L131" si="22">E102-K102</f>
         <v>0</v>
       </c>
       <c r="M102" s="10"/>
@@ -10446,16 +10511,16 @@
         <v>0</v>
       </c>
       <c r="S102" s="10">
-        <f t="shared" ref="S102:S131" si="26">E102/5</f>
+        <f t="shared" ref="S102:S131" si="23">E102/5</f>
         <v>0</v>
       </c>
       <c r="T102" s="12"/>
       <c r="U102" s="10" t="e">
-        <f t="shared" ref="U102:U133" si="27">(F102+O102+P102+Q102+R102+T102)/S102</f>
+        <f t="shared" ref="U102:U131" si="24">(F102+O102+P102+Q102+R102+T102)/S102</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V102" s="10" t="e">
-        <f t="shared" ref="V102:V131" si="28">(F102+O102+P102+Q102+R102)/S102</f>
+        <f t="shared" ref="V102:V131" si="25">(F102+O102+P102+Q102+R102)/S102</f>
         <v>#DIV/0!</v>
       </c>
       <c r="W102" s="10">
@@ -10465,9 +10530,12 @@
         <v>0</v>
       </c>
       <c r="Y102" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z102" s="10"/>
+        <v>166</v>
+      </c>
+      <c r="Z102" s="1">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
       <c r="AA102" s="1"/>
       <c r="AB102" s="1"/>
       <c r="AC102" s="1"/>
@@ -10494,10 +10562,10 @@
     </row>
     <row r="103" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A103" s="16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
@@ -10510,14 +10578,14 @@
         <v>45</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J103" s="1"/>
       <c r="K103" s="1">
         <v>9</v>
       </c>
       <c r="L103" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-9</v>
       </c>
       <c r="M103" s="1"/>
@@ -10533,16 +10601,16 @@
         <v>30</v>
       </c>
       <c r="S103" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="T103" s="5"/>
       <c r="U103" s="1" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V103" s="1" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W103" s="1">
@@ -10553,7 +10621,7 @@
       </c>
       <c r="Y103" s="1"/>
       <c r="Z103" s="1">
-        <f t="shared" ref="Z103:Z108" si="29">G103*T103</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA103" s="1"/>
@@ -10582,10 +10650,10 @@
     </row>
     <row r="104" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A104" s="16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C104" s="1">
         <v>31</v>
@@ -10606,14 +10674,14 @@
         <v>45</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J104" s="1"/>
       <c r="K104" s="1">
         <v>34</v>
       </c>
       <c r="L104" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M104" s="1"/>
@@ -10629,19 +10697,19 @@
         <v>0</v>
       </c>
       <c r="S104" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>6.8</v>
       </c>
       <c r="T104" s="5">
-        <f t="shared" ref="T103:T108" si="30">12*S104-R104-Q104-P104-O104-F104</f>
+        <f t="shared" ref="T104" si="26">12*S104-R104-Q104-P104-O104-F104</f>
         <v>5.7756838905775041</v>
       </c>
       <c r="U104" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>12</v>
       </c>
       <c r="V104" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>11.150634721973894</v>
       </c>
       <c r="W104" s="1">
@@ -10652,8 +10720,8 @@
       </c>
       <c r="Y104" s="1"/>
       <c r="Z104" s="1">
-        <f t="shared" si="29"/>
-        <v>0.46205471124620034</v>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA104" s="1"/>
       <c r="AB104" s="1"/>
@@ -10681,10 +10749,10 @@
     </row>
     <row r="105" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A105" s="16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="1"/>
@@ -10697,12 +10765,12 @@
         <v>30</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J105" s="1"/>
       <c r="K105" s="1"/>
       <c r="L105" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M105" s="1"/>
@@ -10718,16 +10786,16 @@
         <v>0</v>
       </c>
       <c r="S105" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="T105" s="5"/>
       <c r="U105" s="1" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V105" s="1" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W105" s="1">
@@ -10738,7 +10806,7 @@
       </c>
       <c r="Y105" s="1"/>
       <c r="Z105" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA105" s="1"/>
@@ -10767,10 +10835,10 @@
     </row>
     <row r="106" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A106" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
@@ -10783,14 +10851,14 @@
         <v>40</v>
       </c>
       <c r="I106" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J106" s="1"/>
       <c r="K106" s="1">
         <v>17.899999999999999</v>
       </c>
       <c r="L106" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-17.899999999999999</v>
       </c>
       <c r="M106" s="1"/>
@@ -10806,16 +10874,16 @@
         <v>200</v>
       </c>
       <c r="S106" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="T106" s="5"/>
       <c r="U106" s="1" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V106" s="1" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W106" s="1">
@@ -10826,7 +10894,7 @@
       </c>
       <c r="Y106" s="1"/>
       <c r="Z106" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA106" s="1"/>
@@ -10855,10 +10923,10 @@
     </row>
     <row r="107" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A107" s="16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="1">
@@ -10877,14 +10945,14 @@
         <v>40</v>
       </c>
       <c r="I107" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J107" s="1"/>
       <c r="K107" s="1">
         <v>44.4</v>
       </c>
       <c r="L107" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-4.7959999999999994</v>
       </c>
       <c r="M107" s="1"/>
@@ -10902,16 +10970,16 @@
         <v>0</v>
       </c>
       <c r="S107" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>7.9207999999999998</v>
       </c>
       <c r="T107" s="5"/>
       <c r="U107" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>25.197203951773218</v>
       </c>
       <c r="V107" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>25.197203951773218</v>
       </c>
       <c r="W107" s="1">
@@ -10922,7 +10990,7 @@
       </c>
       <c r="Y107" s="1"/>
       <c r="Z107" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA107" s="1"/>
@@ -10951,10 +11019,10 @@
     </row>
     <row r="108" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A108" s="16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="1"/>
@@ -10967,14 +11035,14 @@
         <v>40</v>
       </c>
       <c r="I108" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J108" s="1"/>
       <c r="K108" s="1">
         <v>1.5</v>
       </c>
       <c r="L108" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-1.5</v>
       </c>
       <c r="M108" s="1"/>
@@ -10992,16 +11060,16 @@
         <v>200</v>
       </c>
       <c r="S108" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="T108" s="5"/>
       <c r="U108" s="1" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V108" s="1" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W108" s="1">
@@ -11012,7 +11080,7 @@
       </c>
       <c r="Y108" s="1"/>
       <c r="Z108" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA108" s="1"/>
@@ -11041,10 +11109,10 @@
     </row>
     <row r="109" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A109" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B109" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="10"/>
@@ -11055,12 +11123,12 @@
       </c>
       <c r="H109" s="10"/>
       <c r="I109" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J109" s="10"/>
       <c r="K109" s="10"/>
       <c r="L109" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M109" s="10"/>
@@ -11074,16 +11142,16 @@
         <v>0</v>
       </c>
       <c r="S109" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="T109" s="12"/>
       <c r="U109" s="10" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V109" s="10" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W109" s="10">
@@ -11093,9 +11161,12 @@
         <v>0</v>
       </c>
       <c r="Y109" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z109" s="10"/>
+        <v>34</v>
+      </c>
+      <c r="Z109" s="1">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
       <c r="AA109" s="1"/>
       <c r="AB109" s="1"/>
       <c r="AC109" s="1"/>
@@ -11122,10 +11193,10 @@
     </row>
     <row r="110" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A110" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B110" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C110" s="10"/>
       <c r="D110" s="10"/>
@@ -11136,12 +11207,12 @@
       </c>
       <c r="H110" s="10"/>
       <c r="I110" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J110" s="10"/>
       <c r="K110" s="10"/>
       <c r="L110" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M110" s="10"/>
@@ -11155,16 +11226,16 @@
         <v>0</v>
       </c>
       <c r="S110" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="T110" s="12"/>
       <c r="U110" s="10" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V110" s="10" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W110" s="10">
@@ -11174,9 +11245,12 @@
         <v>0</v>
       </c>
       <c r="Y110" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z110" s="10"/>
+        <v>34</v>
+      </c>
+      <c r="Z110" s="1">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
       <c r="AA110" s="1"/>
       <c r="AB110" s="1"/>
       <c r="AC110" s="1"/>
@@ -11203,10 +11277,10 @@
     </row>
     <row r="111" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A111" s="16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
@@ -11219,14 +11293,14 @@
         <v>40</v>
       </c>
       <c r="I111" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J111" s="1"/>
       <c r="K111" s="1">
         <v>2</v>
       </c>
       <c r="L111" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-2</v>
       </c>
       <c r="M111" s="1"/>
@@ -11242,16 +11316,16 @@
         <v>150</v>
       </c>
       <c r="S111" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="T111" s="5"/>
       <c r="U111" s="1" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V111" s="1" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W111" s="1">
@@ -11262,7 +11336,7 @@
       </c>
       <c r="Y111" s="1"/>
       <c r="Z111" s="1">
-        <f t="shared" ref="Z111:Z130" si="31">G111*T111</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA111" s="1"/>
@@ -11291,10 +11365,10 @@
     </row>
     <row r="112" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A112" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C112" s="1"/>
       <c r="D112" s="1">
@@ -11313,14 +11387,14 @@
         <v>40</v>
       </c>
       <c r="I112" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J112" s="1"/>
       <c r="K112" s="1">
         <v>83</v>
       </c>
       <c r="L112" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-7</v>
       </c>
       <c r="M112" s="1"/>
@@ -11336,16 +11410,16 @@
         <v>0</v>
       </c>
       <c r="S112" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>15.2</v>
       </c>
       <c r="T112" s="5"/>
       <c r="U112" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>14.736842105263159</v>
       </c>
       <c r="V112" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>14.736842105263159</v>
       </c>
       <c r="W112" s="1">
@@ -11356,7 +11430,7 @@
       </c>
       <c r="Y112" s="1"/>
       <c r="Z112" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA112" s="1"/>
@@ -11385,10 +11459,10 @@
     </row>
     <row r="113" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A113" s="16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
@@ -11401,14 +11475,14 @@
         <v>40</v>
       </c>
       <c r="I113" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J113" s="1"/>
       <c r="K113" s="1">
         <v>8</v>
       </c>
       <c r="L113" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-8</v>
       </c>
       <c r="M113" s="1"/>
@@ -11426,16 +11500,16 @@
         <v>150</v>
       </c>
       <c r="S113" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="T113" s="5"/>
       <c r="U113" s="1" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V113" s="1" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W113" s="1">
@@ -11446,7 +11520,7 @@
       </c>
       <c r="Y113" s="1"/>
       <c r="Z113" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA113" s="1"/>
@@ -11475,10 +11549,10 @@
     </row>
     <row r="114" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A114" s="16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C114" s="1">
         <v>28</v>
@@ -11497,14 +11571,14 @@
         <v>45</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J114" s="1"/>
       <c r="K114" s="1">
         <v>15</v>
       </c>
       <c r="L114" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M114" s="1"/>
@@ -11520,19 +11594,19 @@
         <v>0</v>
       </c>
       <c r="S114" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>3</v>
       </c>
       <c r="T114" s="5">
-        <f t="shared" ref="T111:T130" si="32">12*S114-R114-Q114-P114-O114-F114</f>
+        <f t="shared" ref="T114:T130" si="27">12*S114-R114-Q114-P114-O114-F114</f>
         <v>17.033472803347284</v>
       </c>
       <c r="U114" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>12</v>
       </c>
       <c r="V114" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>6.3221757322175725</v>
       </c>
       <c r="W114" s="1">
@@ -11543,8 +11617,8 @@
       </c>
       <c r="Y114" s="1"/>
       <c r="Z114" s="1">
-        <f t="shared" si="31"/>
-        <v>1.5330125523012554</v>
+        <f t="shared" si="18"/>
+        <v>2</v>
       </c>
       <c r="AA114" s="1"/>
       <c r="AB114" s="1"/>
@@ -11572,10 +11646,10 @@
     </row>
     <row r="115" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A115" s="16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="1">
@@ -11594,14 +11668,14 @@
         <v>60</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J115" s="1"/>
       <c r="K115" s="1">
         <v>25</v>
       </c>
       <c r="L115" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-10</v>
       </c>
       <c r="M115" s="1"/>
@@ -11617,19 +11691,19 @@
         <v>0</v>
       </c>
       <c r="S115" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>3</v>
       </c>
       <c r="T115" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="27"/>
         <v>20.856000000000002</v>
       </c>
       <c r="U115" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>12</v>
       </c>
       <c r="V115" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>5.048</v>
       </c>
       <c r="W115" s="1">
@@ -11640,8 +11714,8 @@
       </c>
       <c r="Y115" s="1"/>
       <c r="Z115" s="1">
-        <f t="shared" si="31"/>
-        <v>20.856000000000002</v>
+        <f t="shared" si="18"/>
+        <v>21</v>
       </c>
       <c r="AA115" s="1"/>
       <c r="AB115" s="1"/>
@@ -11669,10 +11743,10 @@
     </row>
     <row r="116" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A116" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="1">
@@ -11691,14 +11765,14 @@
         <v>50</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J116" s="1"/>
       <c r="K116" s="1">
         <v>12.5</v>
       </c>
       <c r="L116" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>9.0000000000003411E-3</v>
       </c>
       <c r="M116" s="1"/>
@@ -11714,16 +11788,16 @@
         <v>0</v>
       </c>
       <c r="S116" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>2.5018000000000002</v>
       </c>
       <c r="T116" s="5"/>
       <c r="U116" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>18.926772723638976</v>
       </c>
       <c r="V116" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>18.926772723638976</v>
       </c>
       <c r="W116" s="1">
@@ -11734,7 +11808,7 @@
       </c>
       <c r="Y116" s="1"/>
       <c r="Z116" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA116" s="1"/>
@@ -11763,10 +11837,10 @@
     </row>
     <row r="117" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A117" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C117" s="1">
         <v>29</v>
@@ -11783,14 +11857,14 @@
         <v>45</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J117" s="1"/>
       <c r="K117" s="1">
         <v>34</v>
       </c>
       <c r="L117" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-25</v>
       </c>
       <c r="M117" s="1"/>
@@ -11806,18 +11880,18 @@
         <v>0</v>
       </c>
       <c r="S117" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>1.8</v>
       </c>
       <c r="T117" s="5">
         <v>10</v>
       </c>
       <c r="U117" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>36.333333333333336</v>
       </c>
       <c r="V117" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>30.777777777777779</v>
       </c>
       <c r="W117" s="1">
@@ -11828,8 +11902,8 @@
       </c>
       <c r="Y117" s="1"/>
       <c r="Z117" s="1">
-        <f t="shared" si="31"/>
-        <v>0.89999999999999991</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="AA117" s="1"/>
       <c r="AB117" s="1"/>
@@ -11857,10 +11931,10 @@
     </row>
     <row r="118" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A118" s="16" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C118" s="1">
         <v>29</v>
@@ -11879,14 +11953,14 @@
         <v>45</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J118" s="1"/>
       <c r="K118" s="1">
         <v>14</v>
       </c>
       <c r="L118" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M118" s="1"/>
@@ -11902,19 +11976,19 @@
         <v>0</v>
       </c>
       <c r="S118" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>2.8</v>
       </c>
       <c r="T118" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="27"/>
         <v>13.068292682926824</v>
       </c>
       <c r="U118" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>11.999999999999998</v>
       </c>
       <c r="V118" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>7.3327526132404186</v>
       </c>
       <c r="W118" s="1">
@@ -11925,8 +11999,8 @@
       </c>
       <c r="Y118" s="1"/>
       <c r="Z118" s="1">
-        <f t="shared" si="31"/>
-        <v>1.1761463414634141</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="AA118" s="1"/>
       <c r="AB118" s="1"/>
@@ -11954,10 +12028,10 @@
     </row>
     <row r="119" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A119" s="16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C119" s="1">
         <v>35.747</v>
@@ -11976,14 +12050,14 @@
         <v>60</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J119" s="1"/>
       <c r="K119" s="1">
         <v>10.1</v>
       </c>
       <c r="L119" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0.87800000000000011</v>
       </c>
       <c r="M119" s="1"/>
@@ -11999,16 +12073,16 @@
         <v>50</v>
       </c>
       <c r="S119" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>2.1955999999999998</v>
       </c>
       <c r="T119" s="5"/>
       <c r="U119" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>39.094747014114979</v>
       </c>
       <c r="V119" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>39.094747014114979</v>
       </c>
       <c r="W119" s="1">
@@ -12019,7 +12093,7 @@
       </c>
       <c r="Y119" s="1"/>
       <c r="Z119" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA119" s="1"/>
@@ -12048,10 +12122,10 @@
     </row>
     <row r="120" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A120" s="16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C120" s="1">
         <v>158.113</v>
@@ -12072,14 +12146,14 @@
         <v>60</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J120" s="1"/>
       <c r="K120" s="1">
         <v>74.400000000000006</v>
       </c>
       <c r="L120" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-12.495000000000005</v>
       </c>
       <c r="M120" s="1"/>
@@ -12095,16 +12169,16 @@
         <v>70</v>
       </c>
       <c r="S120" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>12.381</v>
       </c>
       <c r="T120" s="5"/>
       <c r="U120" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>17.2414183022373</v>
       </c>
       <c r="V120" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>17.2414183022373</v>
       </c>
       <c r="W120" s="1">
@@ -12115,7 +12189,7 @@
       </c>
       <c r="Y120" s="1"/>
       <c r="Z120" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA120" s="1"/>
@@ -12144,10 +12218,10 @@
     </row>
     <row r="121" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A121" s="16" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C121" s="1">
         <v>14.954000000000001</v>
@@ -12168,14 +12242,14 @@
         <v>60</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J121" s="1"/>
       <c r="K121" s="1">
         <v>9.5</v>
       </c>
       <c r="L121" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-2.806</v>
       </c>
       <c r="M121" s="1"/>
@@ -12191,16 +12265,16 @@
         <v>0</v>
       </c>
       <c r="S121" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>1.3388</v>
       </c>
       <c r="T121" s="5"/>
       <c r="U121" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>16.540035853002692</v>
       </c>
       <c r="V121" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>16.540035853002692</v>
       </c>
       <c r="W121" s="1">
@@ -12211,7 +12285,7 @@
       </c>
       <c r="Y121" s="1"/>
       <c r="Z121" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA121" s="1"/>
@@ -12240,10 +12314,10 @@
     </row>
     <row r="122" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A122" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C122" s="1">
         <v>97.364000000000004</v>
@@ -12266,14 +12340,14 @@
         <v>60</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J122" s="1"/>
       <c r="K122" s="1">
         <v>415</v>
       </c>
       <c r="L122" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-62.491999999999962</v>
       </c>
       <c r="M122" s="1"/>
@@ -12289,16 +12363,16 @@
         <v>187.0712</v>
       </c>
       <c r="S122" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>70.50160000000001</v>
       </c>
       <c r="T122" s="5"/>
       <c r="U122" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>19.058761786966535</v>
       </c>
       <c r="V122" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>19.058761786966535</v>
       </c>
       <c r="W122" s="1">
@@ -12309,7 +12383,7 @@
       </c>
       <c r="Y122" s="1"/>
       <c r="Z122" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA122" s="1"/>
@@ -12338,10 +12412,10 @@
     </row>
     <row r="123" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A123" s="16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C123" s="1">
         <v>228</v>
@@ -12360,14 +12434,14 @@
         <v>1096</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J123" s="1"/>
       <c r="K123" s="1">
         <v>15</v>
       </c>
       <c r="L123" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M123" s="1"/>
@@ -12383,16 +12457,16 @@
         <v>0</v>
       </c>
       <c r="S123" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>3</v>
       </c>
       <c r="T123" s="5"/>
       <c r="U123" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>86</v>
       </c>
       <c r="V123" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>86</v>
       </c>
       <c r="W123" s="1">
@@ -12402,10 +12476,10 @@
         <v>0.6</v>
       </c>
       <c r="Y123" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Z123" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA123" s="1"/>
@@ -12434,10 +12508,10 @@
     </row>
     <row r="124" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A124" s="16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C124" s="1">
         <v>134</v>
@@ -12458,14 +12532,14 @@
         <v>1096</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J124" s="1"/>
       <c r="K124" s="1">
         <v>21</v>
       </c>
       <c r="L124" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-5</v>
       </c>
       <c r="M124" s="1"/>
@@ -12481,16 +12555,16 @@
         <v>0</v>
       </c>
       <c r="S124" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>3.2</v>
       </c>
       <c r="T124" s="5"/>
       <c r="U124" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>33.75</v>
       </c>
       <c r="V124" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>33.75</v>
       </c>
       <c r="W124" s="1">
@@ -12500,10 +12574,10 @@
         <v>3.4</v>
       </c>
       <c r="Y124" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Z124" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA124" s="1"/>
@@ -12532,10 +12606,10 @@
     </row>
     <row r="125" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A125" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C125" s="1">
         <v>134</v>
@@ -12556,14 +12630,14 @@
         <v>1096</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J125" s="1"/>
       <c r="K125" s="1">
         <v>26</v>
       </c>
       <c r="L125" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-5</v>
       </c>
       <c r="M125" s="1"/>
@@ -12579,16 +12653,16 @@
         <v>0</v>
       </c>
       <c r="S125" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>4.2</v>
       </c>
       <c r="T125" s="5"/>
       <c r="U125" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>25.714285714285712</v>
       </c>
       <c r="V125" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>25.714285714285712</v>
       </c>
       <c r="W125" s="1">
@@ -12598,10 +12672,10 @@
         <v>2.4</v>
       </c>
       <c r="Y125" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Z125" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA125" s="1"/>
@@ -12630,10 +12704,10 @@
     </row>
     <row r="126" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A126" s="16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C126" s="1"/>
       <c r="D126" s="1"/>
@@ -12646,14 +12720,14 @@
         <v>40</v>
       </c>
       <c r="I126" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J126" s="1"/>
       <c r="K126" s="1">
         <v>7</v>
       </c>
       <c r="L126" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-7</v>
       </c>
       <c r="M126" s="1"/>
@@ -12671,16 +12745,16 @@
         <v>80</v>
       </c>
       <c r="S126" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="T126" s="5"/>
       <c r="U126" s="1" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V126" s="1" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W126" s="1">
@@ -12691,7 +12765,7 @@
       </c>
       <c r="Y126" s="1"/>
       <c r="Z126" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA126" s="1"/>
@@ -12720,10 +12794,10 @@
     </row>
     <row r="127" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A127" s="16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
@@ -12736,14 +12810,14 @@
         <v>40</v>
       </c>
       <c r="I127" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J127" s="1"/>
       <c r="K127" s="1">
         <v>7</v>
       </c>
       <c r="L127" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-7</v>
       </c>
       <c r="M127" s="1"/>
@@ -12761,16 +12835,16 @@
         <v>80</v>
       </c>
       <c r="S127" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="T127" s="5"/>
       <c r="U127" s="1" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V127" s="1" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W127" s="1">
@@ -12781,7 +12855,7 @@
       </c>
       <c r="Y127" s="1"/>
       <c r="Z127" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA127" s="1"/>
@@ -12810,10 +12884,10 @@
     </row>
     <row r="128" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A128" s="16" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
@@ -12826,14 +12900,14 @@
         <v>50</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J128" s="1"/>
       <c r="K128" s="1">
         <v>7.5</v>
       </c>
       <c r="L128" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-7.5</v>
       </c>
       <c r="M128" s="1"/>
@@ -12849,16 +12923,16 @@
         <v>0</v>
       </c>
       <c r="S128" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="T128" s="5"/>
       <c r="U128" s="1" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V128" s="1" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W128" s="1">
@@ -12869,7 +12943,7 @@
       </c>
       <c r="Y128" s="1"/>
       <c r="Z128" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA128" s="1"/>
@@ -12898,10 +12972,10 @@
     </row>
     <row r="129" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A129" s="16" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C129" s="1"/>
       <c r="D129" s="1"/>
@@ -12914,14 +12988,14 @@
         <v>40</v>
       </c>
       <c r="I129" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J129" s="1"/>
       <c r="K129" s="1">
         <v>1</v>
       </c>
       <c r="L129" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-1</v>
       </c>
       <c r="M129" s="1"/>
@@ -12939,16 +13013,16 @@
         <v>80</v>
       </c>
       <c r="S129" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="T129" s="5"/>
       <c r="U129" s="1" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V129" s="1" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W129" s="1">
@@ -12959,7 +13033,7 @@
       </c>
       <c r="Y129" s="1"/>
       <c r="Z129" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA129" s="1"/>
@@ -12988,10 +13062,10 @@
     </row>
     <row r="130" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A130" s="16" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C130" s="1"/>
       <c r="D130" s="1">
@@ -13010,14 +13084,14 @@
         <v>45</v>
       </c>
       <c r="I130" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J130" s="1"/>
       <c r="K130" s="1">
         <v>20</v>
       </c>
       <c r="L130" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-5</v>
       </c>
       <c r="M130" s="1"/>
@@ -13033,19 +13107,19 @@
         <v>0</v>
       </c>
       <c r="S130" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>3</v>
       </c>
       <c r="T130" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="27"/>
         <v>9.3333333333333286</v>
       </c>
       <c r="U130" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>12</v>
       </c>
       <c r="V130" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>8.8888888888888911</v>
       </c>
       <c r="W130" s="1">
@@ -13056,8 +13130,8 @@
       </c>
       <c r="Y130" s="1"/>
       <c r="Z130" s="1">
-        <f t="shared" si="31"/>
-        <v>1.1199999999999994</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="AA130" s="1"/>
       <c r="AB130" s="1"/>
@@ -13085,10 +13159,10 @@
     </row>
     <row r="131" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A131" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C131" s="10">
         <v>-15</v>
@@ -13107,16 +13181,16 @@
       </c>
       <c r="H131" s="10"/>
       <c r="I131" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J131" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K131" s="10">
         <v>24</v>
       </c>
       <c r="L131" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-1</v>
       </c>
       <c r="M131" s="10"/>
@@ -13130,16 +13204,16 @@
         <v>0</v>
       </c>
       <c r="S131" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>4.5999999999999996</v>
       </c>
       <c r="T131" s="12"/>
       <c r="U131" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>-8.0434782608695663</v>
       </c>
       <c r="V131" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>-8.0434782608695663</v>
       </c>
       <c r="W131" s="10">
@@ -13149,7 +13223,10 @@
         <v>2.6</v>
       </c>
       <c r="Y131" s="10"/>
-      <c r="Z131" s="10"/>
+      <c r="Z131" s="1">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
       <c r="AA131" s="1"/>
       <c r="AB131" s="1"/>
       <c r="AC131" s="1"/>
